--- a/QA_TestCase_Portfolio.xlsx
+++ b/QA_TestCase_Portfolio.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63D4FAC-AECA-420E-A381-37A3CD9EA187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Result" sheetId="6" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -3136,7 +3136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -4090,7 +4090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4617,6 +4617,246 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4626,207 +4866,6 @@
     <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4866,36 +4905,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4919,21 +4928,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5012,32 +5006,15 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
+        <strike val="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
@@ -5069,9 +5046,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7052,7 +7046,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[QA_TestCase_Portfolio2.xlsx]Test Result!피벗 테이블1</c:name>
+    <c:name>[QA_TestCase_Portfolio.xlsx]Test Result!피벗 테이블1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -12889,7 +12883,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB4DFF61-44ED-449A-9C02-0A4EA28EC071}" name="피벗 테이블1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB4DFF61-44ED-449A-9C02-0A4EA28EC071}" name="피벗 테이블1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="K22:N28" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -13256,7 +13250,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:V96"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
@@ -13273,21 +13267,21 @@
     <col min="22" max="22" width="11.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="181" t="s">
+    <row r="1" spans="1:22">
+      <c r="A1" s="180" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="S1" s="179" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="S1" s="178" t="s">
         <v>229</v>
       </c>
-      <c r="T1" s="179"/>
-      <c r="U1" s="179"/>
-      <c r="V1" s="179"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="280" t="s">
+      <c r="T1" s="178"/>
+      <c r="U1" s="178"/>
+      <c r="V1" s="178"/>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="181" t="s">
         <v>436</v>
       </c>
       <c r="B2" s="31" t="s">
@@ -13310,7 +13304,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22">
       <c r="A3" s="182"/>
       <c r="B3" s="30" t="s">
         <v>139</v>
@@ -13331,7 +13325,7 @@
       </c>
       <c r="V3" s="92"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22">
       <c r="A4" s="182"/>
       <c r="B4" s="2" t="s">
         <v>141</v>
@@ -13352,7 +13346,7 @@
       </c>
       <c r="V4" s="92"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22">
       <c r="A5" s="183" t="s">
         <v>438</v>
       </c>
@@ -13375,7 +13369,7 @@
       </c>
       <c r="V5" s="92"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22">
       <c r="A6" s="183"/>
       <c r="B6" s="30" t="s">
         <v>139</v>
@@ -13396,7 +13390,7 @@
       </c>
       <c r="V6" s="92"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22">
       <c r="A7" s="183"/>
       <c r="B7" s="2" t="s">
         <v>141</v>
@@ -13417,8 +13411,8 @@
       </c>
       <c r="V7" s="92"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="185" t="s">
+    <row r="8" spans="1:22">
+      <c r="A8" s="184" t="s">
         <v>233</v>
       </c>
       <c r="B8" s="31" t="s">
@@ -13440,8 +13434,8 @@
       </c>
       <c r="V8" s="92"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="185"/>
+    <row r="9" spans="1:22">
+      <c r="A9" s="184"/>
       <c r="B9" s="30" t="s">
         <v>139</v>
       </c>
@@ -13461,8 +13455,8 @@
       </c>
       <c r="V9" s="91"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="185"/>
+    <row r="10" spans="1:22">
+      <c r="A10" s="184"/>
       <c r="B10" s="2" t="s">
         <v>141</v>
       </c>
@@ -13482,8 +13476,8 @@
       </c>
       <c r="V10" s="92"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="184" t="s">
+    <row r="11" spans="1:22">
+      <c r="A11" s="185" t="s">
         <v>439</v>
       </c>
       <c r="B11" s="31" t="s">
@@ -13505,8 +13499,8 @@
       </c>
       <c r="V11" s="92"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="184"/>
+    <row r="12" spans="1:22">
+      <c r="A12" s="185"/>
       <c r="B12" s="30" t="s">
         <v>139</v>
       </c>
@@ -13526,8 +13520,8 @@
       </c>
       <c r="V12" s="92"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="184"/>
+    <row r="13" spans="1:22">
+      <c r="A13" s="185"/>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
@@ -13547,8 +13541,8 @@
       </c>
       <c r="V13" s="91"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="181" t="s">
+    <row r="14" spans="1:22">
+      <c r="A14" s="180" t="s">
         <v>140</v>
       </c>
       <c r="B14" s="27" t="s">
@@ -13570,8 +13564,8 @@
       </c>
       <c r="V14" s="92"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+    <row r="15" spans="1:22">
+      <c r="A15" s="180"/>
       <c r="B15" s="29" t="s">
         <v>139</v>
       </c>
@@ -13591,8 +13585,8 @@
       </c>
       <c r="V15" s="92"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="181"/>
+    <row r="16" spans="1:22">
+      <c r="A16" s="180"/>
       <c r="B16" s="28" t="s">
         <v>141</v>
       </c>
@@ -13612,7 +13606,7 @@
       </c>
       <c r="V16" s="92"/>
     </row>
-    <row r="17" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="11:22">
       <c r="S17" s="132" t="s">
         <v>434</v>
       </c>
@@ -13625,7 +13619,7 @@
       </c>
       <c r="V17" s="91"/>
     </row>
-    <row r="18" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="11:22">
       <c r="S18" s="132" t="s">
         <v>434</v>
       </c>
@@ -13638,7 +13632,7 @@
       </c>
       <c r="V18" s="92"/>
     </row>
-    <row r="19" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="11:22">
       <c r="S19" s="132" t="s">
         <v>434</v>
       </c>
@@ -13651,7 +13645,7 @@
       </c>
       <c r="V19" s="92"/>
     </row>
-    <row r="20" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="11:22">
       <c r="S20" s="132" t="s">
         <v>434</v>
       </c>
@@ -13664,11 +13658,11 @@
       </c>
       <c r="V20" s="92"/>
     </row>
-    <row r="21" spans="11:22" x14ac:dyDescent="0.3">
-      <c r="K21" s="180" t="s">
+    <row r="21" spans="11:22">
+      <c r="K21" s="179" t="s">
         <v>237</v>
       </c>
-      <c r="L21" s="180"/>
+      <c r="L21" s="179"/>
       <c r="S21" s="132" t="s">
         <v>434</v>
       </c>
@@ -13683,7 +13677,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="11:22">
       <c r="K22" s="134" t="s">
         <v>236</v>
       </c>
@@ -13702,7 +13696,7 @@
       </c>
       <c r="V22" s="92"/>
     </row>
-    <row r="23" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="11:22">
       <c r="K23" s="134" t="s">
         <v>234</v>
       </c>
@@ -13727,17 +13721,17 @@
       </c>
       <c r="V23" s="92"/>
     </row>
-    <row r="24" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="11:22">
       <c r="K24" s="131" t="s">
         <v>232</v>
       </c>
-      <c r="L24" s="281">
+      <c r="L24">
         <v>5</v>
       </c>
-      <c r="M24" s="281">
+      <c r="M24">
         <v>24</v>
       </c>
-      <c r="N24" s="281">
+      <c r="N24">
         <v>29</v>
       </c>
       <c r="S24" s="132" t="s">
@@ -13752,15 +13746,14 @@
       </c>
       <c r="V24" s="92"/>
     </row>
-    <row r="25" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="11:22">
       <c r="K25" s="131" t="s">
         <v>316</v>
       </c>
-      <c r="L25" s="281"/>
-      <c r="M25" s="281">
+      <c r="M25">
         <v>1</v>
       </c>
-      <c r="N25" s="281">
+      <c r="N25">
         <v>1</v>
       </c>
       <c r="S25" s="132" t="s">
@@ -13775,17 +13768,17 @@
       </c>
       <c r="V25" s="92"/>
     </row>
-    <row r="26" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="11:22">
       <c r="K26" s="131" t="s">
         <v>434</v>
       </c>
-      <c r="L26" s="281">
+      <c r="L26">
         <v>9</v>
       </c>
-      <c r="M26" s="281">
+      <c r="M26">
         <v>31</v>
       </c>
-      <c r="N26" s="281">
+      <c r="N26">
         <v>40</v>
       </c>
       <c r="S26" s="132" t="s">
@@ -13800,17 +13793,17 @@
       </c>
       <c r="V26" s="92"/>
     </row>
-    <row r="27" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="11:22">
       <c r="K27" s="131" t="s">
         <v>435</v>
       </c>
-      <c r="L27" s="281">
+      <c r="L27">
         <v>3</v>
       </c>
-      <c r="M27" s="281">
+      <c r="M27">
         <v>21</v>
       </c>
-      <c r="N27" s="281">
+      <c r="N27">
         <v>24</v>
       </c>
       <c r="S27" s="132" t="s">
@@ -13825,17 +13818,17 @@
       </c>
       <c r="V27" s="92"/>
     </row>
-    <row r="28" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="11:22">
       <c r="K28" s="131" t="s">
         <v>235</v>
       </c>
-      <c r="L28" s="281">
+      <c r="L28">
         <v>17</v>
       </c>
-      <c r="M28" s="281">
+      <c r="M28">
         <v>77</v>
       </c>
-      <c r="N28" s="281">
+      <c r="N28">
         <v>94</v>
       </c>
       <c r="S28" s="132" t="s">
@@ -13850,7 +13843,7 @@
       </c>
       <c r="V28" s="92"/>
     </row>
-    <row r="29" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="11:22">
       <c r="S29" s="132" t="s">
         <v>434</v>
       </c>
@@ -13863,7 +13856,7 @@
       </c>
       <c r="V29" s="92"/>
     </row>
-    <row r="30" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="11:22">
       <c r="S30" s="132" t="s">
         <v>434</v>
       </c>
@@ -13876,7 +13869,7 @@
       </c>
       <c r="V30" s="92"/>
     </row>
-    <row r="31" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="11:22">
       <c r="S31" s="132" t="s">
         <v>434</v>
       </c>
@@ -13889,7 +13882,7 @@
       </c>
       <c r="V31" s="92"/>
     </row>
-    <row r="32" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="11:22">
       <c r="S32" s="132" t="s">
         <v>434</v>
       </c>
@@ -13902,7 +13895,7 @@
       </c>
       <c r="V32" s="92"/>
     </row>
-    <row r="33" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="33" spans="19:22">
       <c r="S33" s="132" t="s">
         <v>434</v>
       </c>
@@ -13915,7 +13908,7 @@
       </c>
       <c r="V33" s="92"/>
     </row>
-    <row r="34" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="19:22">
       <c r="S34" s="132" t="s">
         <v>434</v>
       </c>
@@ -13928,7 +13921,7 @@
       </c>
       <c r="V34" s="92"/>
     </row>
-    <row r="35" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="19:22">
       <c r="S35" s="132" t="s">
         <v>434</v>
       </c>
@@ -13941,7 +13934,7 @@
       </c>
       <c r="V35" s="92"/>
     </row>
-    <row r="36" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="19:22">
       <c r="S36" s="132" t="s">
         <v>434</v>
       </c>
@@ -13954,7 +13947,7 @@
       </c>
       <c r="V36" s="91"/>
     </row>
-    <row r="37" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="19:22">
       <c r="S37" s="132" t="s">
         <v>434</v>
       </c>
@@ -13967,7 +13960,7 @@
       </c>
       <c r="V37" s="92"/>
     </row>
-    <row r="38" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="19:22">
       <c r="S38" s="132" t="s">
         <v>434</v>
       </c>
@@ -13980,7 +13973,7 @@
       </c>
       <c r="V38" s="92"/>
     </row>
-    <row r="39" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="19:22">
       <c r="S39" s="132" t="s">
         <v>434</v>
       </c>
@@ -13993,7 +13986,7 @@
       </c>
       <c r="V39" s="92"/>
     </row>
-    <row r="40" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="19:22">
       <c r="S40" s="132" t="s">
         <v>434</v>
       </c>
@@ -14006,7 +13999,7 @@
       </c>
       <c r="V40" s="92"/>
     </row>
-    <row r="41" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="19:22">
       <c r="S41" s="132" t="s">
         <v>434</v>
       </c>
@@ -14019,7 +14012,7 @@
       </c>
       <c r="V41" s="92"/>
     </row>
-    <row r="42" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="42" spans="19:22">
       <c r="S42" s="132" t="s">
         <v>434</v>
       </c>
@@ -14032,11 +14025,11 @@
       </c>
       <c r="V42" s="92"/>
     </row>
-    <row r="43" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="43" spans="19:22">
       <c r="S43" s="132" t="s">
         <v>437</v>
       </c>
-      <c r="T43" s="278" t="s">
+      <c r="T43" s="165" t="s">
         <v>331</v>
       </c>
       <c r="U43" s="92" t="str">
@@ -14045,11 +14038,11 @@
       </c>
       <c r="V43" s="92"/>
     </row>
-    <row r="44" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="44" spans="19:22">
       <c r="S44" s="132" t="s">
         <v>437</v>
       </c>
-      <c r="T44" s="278" t="s">
+      <c r="T44" s="165" t="s">
         <v>428</v>
       </c>
       <c r="U44" s="92" t="str">
@@ -14058,11 +14051,11 @@
       </c>
       <c r="V44" s="92"/>
     </row>
-    <row r="45" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="45" spans="19:22">
       <c r="S45" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T45" s="278" t="s">
+      <c r="T45" s="165" t="s">
         <v>340</v>
       </c>
       <c r="U45" s="92" t="str">
@@ -14071,11 +14064,11 @@
       </c>
       <c r="V45" s="92"/>
     </row>
-    <row r="46" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="46" spans="19:22">
       <c r="S46" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T46" s="278" t="s">
+      <c r="T46" s="165" t="s">
         <v>345</v>
       </c>
       <c r="U46" s="92" t="str">
@@ -14084,11 +14077,11 @@
       </c>
       <c r="V46" s="92"/>
     </row>
-    <row r="47" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="47" spans="19:22">
       <c r="S47" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T47" s="278" t="s">
+      <c r="T47" s="165" t="s">
         <v>350</v>
       </c>
       <c r="U47" s="92" t="str">
@@ -14097,11 +14090,11 @@
       </c>
       <c r="V47" s="92"/>
     </row>
-    <row r="48" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="48" spans="19:22">
       <c r="S48" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T48" s="278" t="s">
+      <c r="T48" s="165" t="s">
         <v>354</v>
       </c>
       <c r="U48" s="92" t="str">
@@ -14110,11 +14103,11 @@
       </c>
       <c r="V48" s="92"/>
     </row>
-    <row r="49" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="19:22">
       <c r="S49" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T49" s="278" t="s">
+      <c r="T49" s="165" t="s">
         <v>357</v>
       </c>
       <c r="U49" s="92" t="str">
@@ -14123,11 +14116,11 @@
       </c>
       <c r="V49" s="92"/>
     </row>
-    <row r="50" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="19:22">
       <c r="S50" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T50" s="278" t="s">
+      <c r="T50" s="165" t="s">
         <v>361</v>
       </c>
       <c r="U50" s="92" t="str">
@@ -14136,11 +14129,11 @@
       </c>
       <c r="V50" s="92"/>
     </row>
-    <row r="51" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="19:22">
       <c r="S51" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T51" s="278" t="s">
+      <c r="T51" s="165" t="s">
         <v>365</v>
       </c>
       <c r="U51" s="92" t="str">
@@ -14149,11 +14142,11 @@
       </c>
       <c r="V51" s="92"/>
     </row>
-    <row r="52" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="19:22">
       <c r="S52" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T52" s="278" t="s">
+      <c r="T52" s="165" t="s">
         <v>368</v>
       </c>
       <c r="U52" s="92" t="str">
@@ -14162,11 +14155,11 @@
       </c>
       <c r="V52" s="92"/>
     </row>
-    <row r="53" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="19:22">
       <c r="S53" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T53" s="278" t="s">
+      <c r="T53" s="165" t="s">
         <v>371</v>
       </c>
       <c r="U53" s="92" t="str">
@@ -14175,11 +14168,11 @@
       </c>
       <c r="V53" s="92"/>
     </row>
-    <row r="54" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="19:22">
       <c r="S54" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T54" s="278" t="s">
+      <c r="T54" s="165" t="s">
         <v>376</v>
       </c>
       <c r="U54" s="92" t="str">
@@ -14188,11 +14181,11 @@
       </c>
       <c r="V54" s="92"/>
     </row>
-    <row r="55" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="19:22">
       <c r="S55" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T55" s="278" t="s">
+      <c r="T55" s="165" t="s">
         <v>382</v>
       </c>
       <c r="U55" s="92" t="str">
@@ -14201,11 +14194,11 @@
       </c>
       <c r="V55" s="92"/>
     </row>
-    <row r="56" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="19:22">
       <c r="S56" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T56" s="278" t="s">
+      <c r="T56" s="165" t="s">
         <v>385</v>
       </c>
       <c r="U56" s="92" t="str">
@@ -14214,11 +14207,11 @@
       </c>
       <c r="V56" s="92"/>
     </row>
-    <row r="57" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="19:22">
       <c r="S57" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T57" s="278" t="s">
+      <c r="T57" s="165" t="s">
         <v>389</v>
       </c>
       <c r="U57" s="92" t="str">
@@ -14227,11 +14220,11 @@
       </c>
       <c r="V57" s="92"/>
     </row>
-    <row r="58" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="19:22">
       <c r="S58" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T58" s="278" t="s">
+      <c r="T58" s="165" t="s">
         <v>393</v>
       </c>
       <c r="U58" s="92" t="str">
@@ -14240,11 +14233,11 @@
       </c>
       <c r="V58" s="92"/>
     </row>
-    <row r="59" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="19:22">
       <c r="S59" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T59" s="278" t="s">
+      <c r="T59" s="165" t="s">
         <v>397</v>
       </c>
       <c r="U59" s="92" t="str">
@@ -14253,11 +14246,11 @@
       </c>
       <c r="V59" s="92"/>
     </row>
-    <row r="60" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="19:22">
       <c r="S60" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T60" s="278" t="s">
+      <c r="T60" s="165" t="s">
         <v>400</v>
       </c>
       <c r="U60" s="92" t="str">
@@ -14266,11 +14259,11 @@
       </c>
       <c r="V60" s="92"/>
     </row>
-    <row r="61" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="19:22">
       <c r="S61" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T61" s="278" t="s">
+      <c r="T61" s="165" t="s">
         <v>404</v>
       </c>
       <c r="U61" s="92" t="str">
@@ -14279,11 +14272,11 @@
       </c>
       <c r="V61" s="92"/>
     </row>
-    <row r="62" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="19:22">
       <c r="S62" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T62" s="278" t="s">
+      <c r="T62" s="165" t="s">
         <v>408</v>
       </c>
       <c r="U62" s="92" t="str">
@@ -14292,11 +14285,11 @@
       </c>
       <c r="V62" s="92"/>
     </row>
-    <row r="63" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="19:22">
       <c r="S63" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T63" s="279" t="s">
+      <c r="T63" s="176" t="s">
         <v>410</v>
       </c>
       <c r="U63" s="92" t="str">
@@ -14305,11 +14298,11 @@
       </c>
       <c r="V63" s="92"/>
     </row>
-    <row r="64" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="19:22">
       <c r="S64" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T64" s="279" t="s">
+      <c r="T64" s="176" t="s">
         <v>414</v>
       </c>
       <c r="U64" s="92" t="str">
@@ -14318,11 +14311,11 @@
       </c>
       <c r="V64" s="92"/>
     </row>
-    <row r="65" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="19:22">
       <c r="S65" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T65" s="279" t="s">
+      <c r="T65" s="176" t="s">
         <v>418</v>
       </c>
       <c r="U65" s="92" t="str">
@@ -14331,11 +14324,11 @@
       </c>
       <c r="V65" s="92"/>
     </row>
-    <row r="66" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="19:22">
       <c r="S66" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T66" s="279" t="s">
+      <c r="T66" s="176" t="s">
         <v>422</v>
       </c>
       <c r="U66" s="92" t="str">
@@ -14344,7 +14337,7 @@
       </c>
       <c r="V66" s="92"/>
     </row>
-    <row r="67" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="19:22">
       <c r="S67" s="132" t="s">
         <v>232</v>
       </c>
@@ -14357,7 +14350,7 @@
       </c>
       <c r="V67" s="92"/>
     </row>
-    <row r="68" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="19:22">
       <c r="S68" s="132" t="s">
         <v>232</v>
       </c>
@@ -14370,7 +14363,7 @@
       </c>
       <c r="V68" s="92"/>
     </row>
-    <row r="69" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="19:22">
       <c r="S69" s="132" t="s">
         <v>232</v>
       </c>
@@ -14383,7 +14376,7 @@
       </c>
       <c r="V69" s="92"/>
     </row>
-    <row r="70" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="19:22">
       <c r="S70" s="132" t="s">
         <v>232</v>
       </c>
@@ -14396,7 +14389,7 @@
       </c>
       <c r="V70" s="91"/>
     </row>
-    <row r="71" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="19:22">
       <c r="S71" s="132" t="s">
         <v>232</v>
       </c>
@@ -14409,7 +14402,7 @@
       </c>
       <c r="V71" s="92"/>
     </row>
-    <row r="72" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="19:22">
       <c r="S72" s="132" t="s">
         <v>232</v>
       </c>
@@ -14422,7 +14415,7 @@
       </c>
       <c r="V72" s="92"/>
     </row>
-    <row r="73" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="19:22">
       <c r="S73" s="132" t="s">
         <v>232</v>
       </c>
@@ -14435,7 +14428,7 @@
       </c>
       <c r="V73" s="92"/>
     </row>
-    <row r="74" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="19:22">
       <c r="S74" s="132" t="s">
         <v>232</v>
       </c>
@@ -14448,7 +14441,7 @@
       </c>
       <c r="V74" s="91"/>
     </row>
-    <row r="75" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="19:22">
       <c r="S75" s="132" t="s">
         <v>232</v>
       </c>
@@ -14461,7 +14454,7 @@
       </c>
       <c r="V75" s="92"/>
     </row>
-    <row r="76" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="19:22">
       <c r="S76" s="132" t="s">
         <v>232</v>
       </c>
@@ -14474,7 +14467,7 @@
       </c>
       <c r="V76" s="92"/>
     </row>
-    <row r="77" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="19:22">
       <c r="S77" s="132" t="s">
         <v>232</v>
       </c>
@@ -14487,7 +14480,7 @@
       </c>
       <c r="V77" s="92"/>
     </row>
-    <row r="78" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="19:22">
       <c r="S78" s="132" t="s">
         <v>233</v>
       </c>
@@ -14500,7 +14493,7 @@
       </c>
       <c r="V78" s="92"/>
     </row>
-    <row r="79" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="19:22">
       <c r="S79" s="132" t="s">
         <v>232</v>
       </c>
@@ -14513,7 +14506,7 @@
       </c>
       <c r="V79" s="92"/>
     </row>
-    <row r="80" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="19:22">
       <c r="S80" s="132" t="s">
         <v>232</v>
       </c>
@@ -14526,7 +14519,7 @@
       </c>
       <c r="V80" s="92"/>
     </row>
-    <row r="81" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="81" spans="19:22">
       <c r="S81" s="132" t="s">
         <v>232</v>
       </c>
@@ -14539,7 +14532,7 @@
       </c>
       <c r="V81" s="91"/>
     </row>
-    <row r="82" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="19:22">
       <c r="S82" s="132" t="s">
         <v>232</v>
       </c>
@@ -14552,7 +14545,7 @@
       </c>
       <c r="V82" s="92"/>
     </row>
-    <row r="83" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="83" spans="19:22">
       <c r="S83" s="132" t="s">
         <v>232</v>
       </c>
@@ -14565,7 +14558,7 @@
       </c>
       <c r="V83" s="92"/>
     </row>
-    <row r="84" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="84" spans="19:22">
       <c r="S84" s="132" t="s">
         <v>232</v>
       </c>
@@ -14578,7 +14571,7 @@
       </c>
       <c r="V84" s="92"/>
     </row>
-    <row r="85" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="85" spans="19:22">
       <c r="S85" s="132" t="s">
         <v>232</v>
       </c>
@@ -14591,7 +14584,7 @@
       </c>
       <c r="V85" s="92"/>
     </row>
-    <row r="86" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="86" spans="19:22">
       <c r="S86" s="132" t="s">
         <v>232</v>
       </c>
@@ -14604,7 +14597,7 @@
       </c>
       <c r="V86" s="92"/>
     </row>
-    <row r="87" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="87" spans="19:22">
       <c r="S87" s="132" t="s">
         <v>232</v>
       </c>
@@ -14617,7 +14610,7 @@
       </c>
       <c r="V87" s="92"/>
     </row>
-    <row r="88" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="88" spans="19:22">
       <c r="S88" s="132" t="s">
         <v>232</v>
       </c>
@@ -14630,7 +14623,7 @@
       </c>
       <c r="V88" s="92"/>
     </row>
-    <row r="89" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="89" spans="19:22">
       <c r="S89" s="132" t="s">
         <v>232</v>
       </c>
@@ -14643,7 +14636,7 @@
       </c>
       <c r="V89" s="92"/>
     </row>
-    <row r="90" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="90" spans="19:22">
       <c r="S90" s="132" t="s">
         <v>232</v>
       </c>
@@ -14656,7 +14649,7 @@
       </c>
       <c r="V90" s="92"/>
     </row>
-    <row r="91" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="91" spans="19:22">
       <c r="S91" s="132" t="s">
         <v>232</v>
       </c>
@@ -14669,7 +14662,7 @@
       </c>
       <c r="V91" s="92"/>
     </row>
-    <row r="92" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="92" spans="19:22">
       <c r="S92" s="132" t="s">
         <v>232</v>
       </c>
@@ -14682,7 +14675,7 @@
       </c>
       <c r="V92" s="92"/>
     </row>
-    <row r="93" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="93" spans="19:22">
       <c r="S93" s="132" t="s">
         <v>232</v>
       </c>
@@ -14695,7 +14688,7 @@
       </c>
       <c r="V93" s="92"/>
     </row>
-    <row r="94" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="94" spans="19:22">
       <c r="S94" s="132" t="s">
         <v>232</v>
       </c>
@@ -14708,7 +14701,7 @@
       </c>
       <c r="V94" s="92"/>
     </row>
-    <row r="95" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="95" spans="19:22">
       <c r="S95" s="132" t="s">
         <v>232</v>
       </c>
@@ -14721,7 +14714,7 @@
       </c>
       <c r="V95" s="92"/>
     </row>
-    <row r="96" spans="19:22" x14ac:dyDescent="0.3">
+    <row r="96" spans="19:22">
       <c r="S96" s="132" t="s">
         <v>241</v>
       </c>
@@ -14763,7 +14756,7 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:V95"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -14773,12 +14766,12 @@
     <col min="22" max="22" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="87.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="188" t="s">
+    <row r="1" spans="1:21" ht="87.75" thickBot="1">
+      <c r="A1" s="250" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="190"/>
+      <c r="B1" s="251"/>
+      <c r="C1" s="252"/>
       <c r="D1" s="6" t="s">
         <v>17</v>
       </c>
@@ -14834,11 +14827,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="202" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="236" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="209" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -14879,8 +14872,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="203"/>
+    <row r="3" spans="1:21">
+      <c r="A3" s="237"/>
       <c r="B3" s="182"/>
       <c r="C3" s="5" t="s">
         <v>1</v>
@@ -14918,9 +14911,9 @@
       <c r="T3" s="17"/>
       <c r="U3" s="17"/>
     </row>
-    <row r="4" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="204"/>
-      <c r="B4" s="206"/>
+    <row r="4" spans="1:21" ht="17.25" thickBot="1">
+      <c r="A4" s="238"/>
+      <c r="B4" s="210"/>
       <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
@@ -14949,8 +14942,8 @@
       </c>
       <c r="U4" s="18"/>
     </row>
-    <row r="5" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="199" t="s">
+    <row r="5" spans="1:21" ht="16.5" customHeight="1">
+      <c r="A5" s="233" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="48" t="s">
@@ -14984,8 +14977,8 @@
       </c>
       <c r="U5" s="19"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="200"/>
+    <row r="6" spans="1:21">
+      <c r="A6" s="234"/>
       <c r="B6" s="183" t="s">
         <v>9</v>
       </c>
@@ -15013,8 +15006,8 @@
       <c r="T6" s="17"/>
       <c r="U6" s="17"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="200"/>
+    <row r="7" spans="1:21">
+      <c r="A7" s="234"/>
       <c r="B7" s="183"/>
       <c r="C7" s="3" t="s">
         <v>11</v>
@@ -15040,8 +15033,8 @@
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="200"/>
+    <row r="8" spans="1:21">
+      <c r="A8" s="234"/>
       <c r="B8" s="183" t="s">
         <v>5</v>
       </c>
@@ -15069,8 +15062,8 @@
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="200"/>
+    <row r="9" spans="1:21">
+      <c r="A9" s="234"/>
       <c r="B9" s="183"/>
       <c r="C9" s="3" t="s">
         <v>11</v>
@@ -15096,8 +15089,8 @@
       <c r="T9" s="17"/>
       <c r="U9" s="17"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="200"/>
+    <row r="10" spans="1:21">
+      <c r="A10" s="234"/>
       <c r="B10" s="183" t="s">
         <v>8</v>
       </c>
@@ -15127,8 +15120,8 @@
       <c r="T10" s="17"/>
       <c r="U10" s="17"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="200"/>
+    <row r="11" spans="1:21">
+      <c r="A11" s="234"/>
       <c r="B11" s="183"/>
       <c r="C11" s="3" t="s">
         <v>11</v>
@@ -15154,8 +15147,8 @@
       <c r="T11" s="17"/>
       <c r="U11" s="17"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="200"/>
+    <row r="12" spans="1:21">
+      <c r="A12" s="234"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -15183,8 +15176,8 @@
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="200"/>
+    <row r="13" spans="1:21">
+      <c r="A13" s="234"/>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
@@ -15212,8 +15205,8 @@
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="200"/>
+    <row r="14" spans="1:21">
+      <c r="A14" s="234"/>
       <c r="B14" s="2" t="s">
         <v>4</v>
       </c>
@@ -15241,8 +15234,8 @@
       <c r="T14" s="17"/>
       <c r="U14" s="17"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="200"/>
+    <row r="15" spans="1:21">
+      <c r="A15" s="234"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -15272,8 +15265,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="200"/>
+    <row r="16" spans="1:21">
+      <c r="A16" s="234"/>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
@@ -15301,8 +15294,8 @@
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
     </row>
-    <row r="17" spans="1:22" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="201"/>
+    <row r="17" spans="1:22" ht="33.75" thickBot="1">
+      <c r="A17" s="235"/>
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
@@ -15332,14 +15325,14 @@
       <c r="T17" s="20"/>
       <c r="U17" s="20"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="196" t="s">
+    <row r="18" spans="1:22">
+      <c r="A18" s="230" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="191" t="s">
+      <c r="B18" s="253" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="191"/>
+      <c r="C18" s="253"/>
       <c r="D18" s="16" t="s">
         <v>102</v>
       </c>
@@ -15395,12 +15388,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="197"/>
-      <c r="B19" s="192" t="s">
+    <row r="19" spans="1:22" ht="32.25" customHeight="1">
+      <c r="A19" s="231"/>
+      <c r="B19" s="254" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="192"/>
+      <c r="C19" s="254"/>
       <c r="D19" s="17" t="s">
         <v>102</v>
       </c>
@@ -15452,12 +15445,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="198"/>
-      <c r="B20" s="193" t="s">
+    <row r="20" spans="1:22" ht="17.25" thickBot="1">
+      <c r="A20" s="232"/>
+      <c r="B20" s="255" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="193"/>
+      <c r="C20" s="255"/>
       <c r="D20" s="18" t="s">
         <v>102</v>
       </c>
@@ -15509,8 +15502,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="209" t="s">
+    <row r="21" spans="1:22">
+      <c r="A21" s="241" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="46" t="s">
@@ -15552,8 +15545,8 @@
       <c r="T21" s="19"/>
       <c r="U21" s="19"/>
     </row>
-    <row r="22" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="210"/>
+    <row r="22" spans="1:22" ht="17.25" thickBot="1">
+      <c r="A22" s="242"/>
       <c r="B22" s="45" t="s">
         <v>21</v>
       </c>
@@ -15597,14 +15590,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="215" t="s">
+    <row r="23" spans="1:22" ht="17.25" thickTop="1">
+      <c r="A23" s="245" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="216" t="s">
+      <c r="B23" s="246" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="216"/>
+      <c r="C23" s="246"/>
       <c r="D23" s="21" t="s">
         <v>102</v>
       </c>
@@ -15648,8 +15641,8 @@
       <c r="T23" s="21"/>
       <c r="U23" s="21"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="200"/>
+    <row r="24" spans="1:22">
+      <c r="A24" s="234"/>
       <c r="B24" s="183" t="s">
         <v>25</v>
       </c>
@@ -15677,12 +15670,12 @@
       </c>
       <c r="U24" s="17"/>
     </row>
-    <row r="25" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="201"/>
-      <c r="B25" s="217" t="s">
+    <row r="25" spans="1:22" ht="17.25" thickBot="1">
+      <c r="A25" s="235"/>
+      <c r="B25" s="247" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="217"/>
+      <c r="C25" s="247"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
@@ -15706,14 +15699,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A26" s="196" t="s">
+    <row r="26" spans="1:22">
+      <c r="A26" s="230" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="211" t="s">
+      <c r="B26" s="192" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="211"/>
+      <c r="C26" s="192"/>
       <c r="D26" s="16" t="s">
         <v>102</v>
       </c>
@@ -15765,12 +15758,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A27" s="214"/>
-      <c r="B27" s="186" t="s">
+    <row r="27" spans="1:22">
+      <c r="A27" s="244"/>
+      <c r="B27" s="248" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="187"/>
+      <c r="C27" s="249"/>
       <c r="D27" s="24" t="s">
         <v>56</v>
       </c>
@@ -15823,12 +15816,12 @@
       </c>
       <c r="V27" s="26"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A28" s="214"/>
-      <c r="B28" s="186" t="s">
+    <row r="28" spans="1:22">
+      <c r="A28" s="244"/>
+      <c r="B28" s="248" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="187"/>
+      <c r="C28" s="249"/>
       <c r="D28" s="17" t="s">
         <v>102</v>
       </c>
@@ -15880,9 +15873,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" s="197"/>
-      <c r="B29" s="207" t="s">
+    <row r="29" spans="1:22">
+      <c r="A29" s="231"/>
+      <c r="B29" s="239" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="14" t="s">
@@ -15931,9 +15924,9 @@
       <c r="T29" s="22"/>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" spans="1:22" ht="33" x14ac:dyDescent="0.3">
-      <c r="A30" s="197"/>
-      <c r="B30" s="208"/>
+    <row r="30" spans="1:22" ht="33">
+      <c r="A30" s="231"/>
+      <c r="B30" s="240"/>
       <c r="C30" s="15" t="s">
         <v>53</v>
       </c>
@@ -15980,12 +15973,12 @@
       <c r="T30" s="22"/>
       <c r="U30" s="22"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A31" s="197"/>
-      <c r="B31" s="212" t="s">
+    <row r="31" spans="1:22">
+      <c r="A31" s="231"/>
+      <c r="B31" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="212"/>
+      <c r="C31" s="198"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -16009,12 +16002,12 @@
       </c>
       <c r="U31" s="17"/>
     </row>
-    <row r="32" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="198"/>
-      <c r="B32" s="213" t="s">
+    <row r="32" spans="1:22" ht="17.25" thickBot="1">
+      <c r="A32" s="232"/>
+      <c r="B32" s="243" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="213"/>
+      <c r="C32" s="243"/>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
       <c r="F32" s="23"/>
@@ -16038,12 +16031,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="194" t="s">
+    <row r="33" spans="1:21" ht="33" customHeight="1" thickBot="1">
+      <c r="A33" s="187" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
+      <c r="B33" s="188"/>
+      <c r="C33" s="188"/>
       <c r="D33" s="102" t="s">
         <v>136</v>
       </c>
@@ -16099,13 +16092,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:21" ht="87" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="227" t="s">
+    <row r="35" spans="1:21" ht="17.25" thickBot="1"/>
+    <row r="36" spans="1:21" ht="87" thickBot="1">
+      <c r="A36" s="221" t="s">
         <v>431</v>
       </c>
-      <c r="B36" s="228"/>
-      <c r="C36" s="229"/>
+      <c r="B36" s="222"/>
+      <c r="C36" s="223"/>
       <c r="D36" s="54" t="s">
         <v>59</v>
       </c>
@@ -16146,11 +16139,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="18" x14ac:dyDescent="0.3">
-      <c r="A37" s="230" t="s">
+    <row r="37" spans="1:21" ht="18">
+      <c r="A37" s="224" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="205" t="s">
+      <c r="B37" s="209" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -16178,8 +16171,8 @@
       <c r="O37" s="32"/>
       <c r="P37" s="55"/>
     </row>
-    <row r="38" spans="1:21" ht="18" x14ac:dyDescent="0.3">
-      <c r="A38" s="231"/>
+    <row r="38" spans="1:21" ht="18">
+      <c r="A38" s="225"/>
       <c r="B38" s="182"/>
       <c r="C38" s="5" t="s">
         <v>1</v>
@@ -16212,9 +16205,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="232"/>
-      <c r="B39" s="206"/>
+    <row r="39" spans="1:21" ht="17.25" thickBot="1">
+      <c r="A39" s="226"/>
+      <c r="B39" s="210"/>
       <c r="C39" s="9" t="s">
         <v>2</v>
       </c>
@@ -16236,8 +16229,8 @@
       </c>
       <c r="P39" s="56"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="233" t="s">
+    <row r="40" spans="1:21">
+      <c r="A40" s="227" t="s">
         <v>31</v>
       </c>
       <c r="B40" s="48" t="s">
@@ -16264,8 +16257,8 @@
       <c r="O40" s="41"/>
       <c r="P40" s="57"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A41" s="234"/>
+    <row r="41" spans="1:21">
+      <c r="A41" s="228"/>
       <c r="B41" s="183" t="s">
         <v>9</v>
       </c>
@@ -16288,8 +16281,8 @@
       <c r="O41" s="39"/>
       <c r="P41" s="52"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="234"/>
+    <row r="42" spans="1:21">
+      <c r="A42" s="228"/>
       <c r="B42" s="183"/>
       <c r="C42" s="3" t="s">
         <v>11</v>
@@ -16310,8 +16303,8 @@
       <c r="O42" s="39"/>
       <c r="P42" s="52"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="234"/>
+    <row r="43" spans="1:21">
+      <c r="A43" s="228"/>
       <c r="B43" s="183" t="s">
         <v>5</v>
       </c>
@@ -16334,8 +16327,8 @@
       <c r="O43" s="39"/>
       <c r="P43" s="52"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A44" s="234"/>
+    <row r="44" spans="1:21">
+      <c r="A44" s="228"/>
       <c r="B44" s="183"/>
       <c r="C44" s="3" t="s">
         <v>11</v>
@@ -16356,8 +16349,8 @@
       <c r="O44" s="39"/>
       <c r="P44" s="52"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="234"/>
+    <row r="45" spans="1:21">
+      <c r="A45" s="228"/>
       <c r="B45" s="183" t="s">
         <v>8</v>
       </c>
@@ -16380,8 +16373,8 @@
       <c r="O45" s="39"/>
       <c r="P45" s="52"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="234"/>
+    <row r="46" spans="1:21">
+      <c r="A46" s="228"/>
       <c r="B46" s="183"/>
       <c r="C46" s="3" t="s">
         <v>11</v>
@@ -16402,8 +16395,8 @@
       <c r="O46" s="39"/>
       <c r="P46" s="52"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A47" s="234"/>
+    <row r="47" spans="1:21">
+      <c r="A47" s="228"/>
       <c r="B47" s="2" t="s">
         <v>4</v>
       </c>
@@ -16426,8 +16419,8 @@
       <c r="O47" s="39"/>
       <c r="P47" s="52"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A48" s="234"/>
+    <row r="48" spans="1:21">
+      <c r="A48" s="228"/>
       <c r="B48" s="2" t="s">
         <v>6</v>
       </c>
@@ -16450,8 +16443,8 @@
       <c r="O48" s="39"/>
       <c r="P48" s="52"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="234"/>
+    <row r="49" spans="1:16">
+      <c r="A49" s="228"/>
       <c r="B49" s="2" t="s">
         <v>7</v>
       </c>
@@ -16474,8 +16467,8 @@
       <c r="O49" s="39"/>
       <c r="P49" s="52"/>
     </row>
-    <row r="50" spans="1:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="235"/>
+    <row r="50" spans="1:16" ht="33.75" thickBot="1">
+      <c r="A50" s="229"/>
       <c r="B50" s="10" t="s">
         <v>15</v>
       </c>
@@ -16500,14 +16493,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" ht="17.25" thickBot="1">
       <c r="A51" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="225" t="s">
+      <c r="B51" s="214" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="225"/>
+      <c r="C51" s="214"/>
       <c r="D51" s="64" t="s">
         <v>102</v>
       </c>
@@ -16548,11 +16541,11 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A52" s="237" t="s">
+    <row r="52" spans="1:16">
+      <c r="A52" s="206" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="243" t="s">
+      <c r="B52" s="215" t="s">
         <v>22</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -16576,9 +16569,9 @@
       <c r="O52" s="32"/>
       <c r="P52" s="55"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" s="238"/>
-      <c r="B53" s="241"/>
+    <row r="53" spans="1:16">
+      <c r="A53" s="207"/>
+      <c r="B53" s="216"/>
       <c r="C53" s="12" t="s">
         <v>75</v>
       </c>
@@ -16600,9 +16593,9 @@
       <c r="O53" s="41"/>
       <c r="P53" s="57"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="238"/>
-      <c r="B54" s="241"/>
+    <row r="54" spans="1:16">
+      <c r="A54" s="207"/>
+      <c r="B54" s="216"/>
       <c r="C54" s="12" t="s">
         <v>73</v>
       </c>
@@ -16624,9 +16617,9 @@
       <c r="O54" s="41"/>
       <c r="P54" s="57"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" s="238"/>
-      <c r="B55" s="244"/>
+    <row r="55" spans="1:16">
+      <c r="A55" s="207"/>
+      <c r="B55" s="217"/>
       <c r="C55" s="12" t="s">
         <v>74</v>
       </c>
@@ -16648,9 +16641,9 @@
       <c r="O55" s="41"/>
       <c r="P55" s="57"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="238"/>
-      <c r="B56" s="240" t="s">
+    <row r="56" spans="1:16">
+      <c r="A56" s="207"/>
+      <c r="B56" s="218" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="12" t="s">
@@ -16674,9 +16667,9 @@
       </c>
       <c r="P56" s="57"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="238"/>
-      <c r="B57" s="241"/>
+    <row r="57" spans="1:16">
+      <c r="A57" s="207"/>
+      <c r="B57" s="216"/>
       <c r="C57" s="12" t="s">
         <v>72</v>
       </c>
@@ -16698,9 +16691,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="238"/>
-      <c r="B58" s="241"/>
+    <row r="58" spans="1:16">
+      <c r="A58" s="207"/>
+      <c r="B58" s="216"/>
       <c r="C58" s="12" t="s">
         <v>73</v>
       </c>
@@ -16722,9 +16715,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="239"/>
-      <c r="B59" s="242"/>
+    <row r="59" spans="1:16" ht="17.25" thickBot="1">
+      <c r="A59" s="208"/>
+      <c r="B59" s="219"/>
       <c r="C59" s="68" t="s">
         <v>74</v>
       </c>
@@ -16746,14 +16739,14 @@
       </c>
       <c r="P59" s="71"/>
     </row>
-    <row r="60" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" ht="17.25" thickBot="1">
       <c r="A60" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="226" t="s">
+      <c r="B60" s="220" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="226"/>
+      <c r="C60" s="220"/>
       <c r="D60" s="19" t="s">
         <v>102</v>
       </c>
@@ -16794,14 +16787,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A61" s="222" t="s">
+    <row r="61" spans="1:16" ht="18">
+      <c r="A61" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="B61" s="211" t="s">
+      <c r="B61" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C61" s="211"/>
+      <c r="C61" s="192"/>
       <c r="D61" s="73" t="s">
         <v>102</v>
       </c>
@@ -16842,8 +16835,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="245"/>
+    <row r="62" spans="1:16" ht="66.75" thickBot="1">
+      <c r="A62" s="211"/>
       <c r="B62" s="4" t="s">
         <v>77</v>
       </c>
@@ -16890,14 +16883,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" ht="18" thickTop="1" thickBot="1">
       <c r="A63" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B63" s="220" t="s">
+      <c r="B63" s="189" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="220"/>
+      <c r="C63" s="189"/>
       <c r="D63" s="49" t="s">
         <v>102</v>
       </c>
@@ -16938,14 +16931,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A64" s="222" t="s">
+    <row r="64" spans="1:16" ht="18">
+      <c r="A64" s="190" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="211" t="s">
+      <c r="B64" s="192" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="211"/>
+      <c r="C64" s="192"/>
       <c r="D64" s="73" t="s">
         <v>102</v>
       </c>
@@ -16986,9 +16979,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A65" s="223"/>
-      <c r="B65" s="218" t="s">
+    <row r="65" spans="1:16" ht="49.5">
+      <c r="A65" s="196"/>
+      <c r="B65" s="212" t="s">
         <v>83</v>
       </c>
       <c r="C65" s="15" t="s">
@@ -17026,9 +17019,9 @@
       <c r="O65" s="39"/>
       <c r="P65" s="52"/>
     </row>
-    <row r="66" spans="1:16" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="224"/>
-      <c r="B66" s="219"/>
+    <row r="66" spans="1:16" ht="50.25" thickBot="1">
+      <c r="A66" s="191"/>
+      <c r="B66" s="213"/>
       <c r="C66" s="53" t="s">
         <v>82</v>
       </c>
@@ -17054,14 +17047,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" ht="17.25" thickBot="1">
       <c r="A67" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B67" s="221" t="s">
+      <c r="B67" s="195" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="221"/>
+      <c r="C67" s="195"/>
       <c r="D67" s="79" t="s">
         <v>102</v>
       </c>
@@ -17090,14 +17083,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" ht="18.75" thickBot="1">
       <c r="A68" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="236" t="s">
+      <c r="B68" s="186" t="s">
         <v>88</v>
       </c>
-      <c r="C68" s="236"/>
+      <c r="C68" s="186"/>
       <c r="D68" s="80" t="s">
         <v>102</v>
       </c>
@@ -17126,12 +17119,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="194" t="s">
+    <row r="69" spans="1:16" ht="17.25" thickBot="1">
+      <c r="A69" s="187" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="195"/>
-      <c r="C69" s="195"/>
+      <c r="B69" s="188"/>
+      <c r="C69" s="188"/>
       <c r="D69" s="102" t="s">
         <v>137</v>
       </c>
@@ -17172,13 +17165,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:16" ht="78" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="259" t="s">
+    <row r="71" spans="1:16" ht="17.25" thickBot="1"/>
+    <row r="72" spans="1:16" ht="78" thickBot="1">
+      <c r="A72" s="203" t="s">
         <v>430</v>
       </c>
-      <c r="B72" s="260"/>
-      <c r="C72" s="261"/>
+      <c r="B72" s="204"/>
+      <c r="C72" s="205"/>
       <c r="D72" s="54" t="s">
         <v>90</v>
       </c>
@@ -17207,11 +17200,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A73" s="237" t="s">
+    <row r="73" spans="1:16">
+      <c r="A73" s="206" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="205" t="s">
+      <c r="B73" s="209" t="s">
         <v>3</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -17233,8 +17226,8 @@
       <c r="K73" s="112"/>
       <c r="L73" s="112"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74" s="238"/>
+    <row r="74" spans="1:16">
+      <c r="A74" s="207"/>
       <c r="B74" s="182"/>
       <c r="C74" s="5" t="s">
         <v>1</v>
@@ -17255,9 +17248,9 @@
       <c r="K74" s="113"/>
       <c r="L74" s="113"/>
     </row>
-    <row r="75" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="238"/>
-      <c r="B75" s="206"/>
+    <row r="75" spans="1:16" ht="17.25" thickBot="1">
+      <c r="A75" s="207"/>
+      <c r="B75" s="210"/>
       <c r="C75" s="9" t="s">
         <v>2</v>
       </c>
@@ -17277,8 +17270,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" s="238"/>
+    <row r="76" spans="1:16">
+      <c r="A76" s="207"/>
       <c r="B76" s="46" t="s">
         <v>14</v>
       </c>
@@ -17301,8 +17294,8 @@
       <c r="K76" s="115"/>
       <c r="L76" s="115"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="238"/>
+    <row r="77" spans="1:16">
+      <c r="A77" s="207"/>
       <c r="B77" s="182" t="s">
         <v>9</v>
       </c>
@@ -17323,8 +17316,8 @@
       </c>
       <c r="L77" s="113"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A78" s="238"/>
+    <row r="78" spans="1:16">
+      <c r="A78" s="207"/>
       <c r="B78" s="182"/>
       <c r="C78" s="5" t="s">
         <v>11</v>
@@ -17343,8 +17336,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="239"/>
+    <row r="79" spans="1:16" ht="33.75" thickBot="1">
+      <c r="A79" s="208"/>
       <c r="B79" s="45" t="s">
         <v>15</v>
       </c>
@@ -17365,8 +17358,8 @@
       <c r="K79" s="116"/>
       <c r="L79" s="116"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A80" s="263" t="s">
+    <row r="80" spans="1:16">
+      <c r="A80" s="199" t="s">
         <v>99</v>
       </c>
       <c r="B80" s="88" t="s">
@@ -17403,8 +17396,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="264"/>
+    <row r="81" spans="1:12">
+      <c r="A81" s="200"/>
       <c r="B81" s="183" t="s">
         <v>212</v>
       </c>
@@ -17425,8 +17418,8 @@
       <c r="K81" s="113"/>
       <c r="L81" s="113"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="264"/>
+    <row r="82" spans="1:12">
+      <c r="A82" s="200"/>
       <c r="B82" s="183" t="s">
         <v>209</v>
       </c>
@@ -17447,8 +17440,8 @@
       </c>
       <c r="L82" s="113"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="264"/>
+    <row r="83" spans="1:12">
+      <c r="A83" s="200"/>
       <c r="B83" s="183" t="s">
         <v>211</v>
       </c>
@@ -17469,12 +17462,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="265"/>
-      <c r="B84" s="262" t="s">
+    <row r="84" spans="1:12" ht="17.25" thickBot="1">
+      <c r="A84" s="201"/>
+      <c r="B84" s="202" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="262"/>
+      <c r="C84" s="202"/>
       <c r="D84" s="114" t="s">
         <v>226</v>
       </c>
@@ -17503,14 +17496,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="223" t="s">
+    <row r="85" spans="1:12">
+      <c r="A85" s="196" t="s">
         <v>19</v>
       </c>
-      <c r="B85" s="268" t="s">
+      <c r="B85" s="197" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="212"/>
+      <c r="C85" s="198"/>
       <c r="D85" s="117" t="s">
         <v>56</v>
       </c>
@@ -17539,8 +17532,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="224"/>
+    <row r="86" spans="1:12" ht="83.25" thickBot="1">
+      <c r="A86" s="191"/>
       <c r="B86" s="111" t="s">
         <v>77</v>
       </c>
@@ -17575,14 +17568,14 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" ht="18" thickTop="1" thickBot="1">
       <c r="A87" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B87" s="220" t="s">
+      <c r="B87" s="189" t="s">
         <v>222</v>
       </c>
-      <c r="C87" s="220"/>
+      <c r="C87" s="189"/>
       <c r="D87" s="121"/>
       <c r="E87" s="122" t="s">
         <v>226</v>
@@ -17605,14 +17598,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="222" t="s">
+    <row r="88" spans="1:12">
+      <c r="A88" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="B88" s="211" t="s">
+      <c r="B88" s="192" t="s">
         <v>223</v>
       </c>
-      <c r="C88" s="211"/>
+      <c r="C88" s="192"/>
       <c r="D88" s="123"/>
       <c r="E88" s="124" t="s">
         <v>226</v>
@@ -17629,8 +17622,8 @@
       </c>
       <c r="L88" s="124"/>
     </row>
-    <row r="89" spans="1:12" ht="99.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="224"/>
+    <row r="89" spans="1:12" ht="99.75" thickBot="1">
+      <c r="A89" s="191"/>
       <c r="B89" s="4" t="s">
         <v>77</v>
       </c>
@@ -17653,14 +17646,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" ht="18" thickTop="1" thickBot="1">
       <c r="A90" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B90" s="220" t="s">
+      <c r="B90" s="189" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="220"/>
+      <c r="C90" s="189"/>
       <c r="D90" s="121"/>
       <c r="E90" s="121"/>
       <c r="F90" s="122" t="s">
@@ -17677,14 +17670,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="222" t="s">
+    <row r="91" spans="1:12">
+      <c r="A91" s="190" t="s">
         <v>84</v>
       </c>
-      <c r="B91" s="211" t="s">
+      <c r="B91" s="192" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="211"/>
+      <c r="C91" s="192"/>
       <c r="D91" s="123"/>
       <c r="E91" s="123"/>
       <c r="F91" s="124" t="s">
@@ -17701,12 +17694,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="224"/>
-      <c r="B92" s="266" t="s">
+    <row r="92" spans="1:12" ht="17.25" thickBot="1">
+      <c r="A92" s="191"/>
+      <c r="B92" s="193" t="s">
         <v>82</v>
       </c>
-      <c r="C92" s="267"/>
+      <c r="C92" s="194"/>
       <c r="D92" s="126"/>
       <c r="E92" s="126"/>
       <c r="F92" s="114" t="s">
@@ -17723,14 +17716,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" ht="17.25" thickBot="1">
       <c r="A93" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B93" s="221" t="s">
+      <c r="B93" s="195" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="221"/>
+      <c r="C93" s="195"/>
       <c r="D93" s="127"/>
       <c r="E93" s="127"/>
       <c r="F93" s="128" t="s">
@@ -17747,14 +17740,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" ht="17.25" thickBot="1">
       <c r="A94" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="B94" s="236" t="s">
+      <c r="B94" s="186" t="s">
         <v>228</v>
       </c>
-      <c r="C94" s="236"/>
+      <c r="C94" s="186"/>
       <c r="D94" s="129"/>
       <c r="E94" s="129"/>
       <c r="F94" s="130" t="s">
@@ -17771,12 +17764,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="194" t="s">
+    <row r="95" spans="1:12" ht="17.25" thickBot="1">
+      <c r="A95" s="187" t="s">
         <v>138</v>
       </c>
-      <c r="B95" s="195"/>
-      <c r="C95" s="195"/>
+      <c r="B95" s="188"/>
+      <c r="C95" s="188"/>
       <c r="D95" s="102" t="s">
         <v>136</v>
       </c>
@@ -17807,48 +17800,14 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="A40:A50"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A5:A17"/>
@@ -17865,52 +17824,86 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="A40:A50"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A33:XFD33">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+  <conditionalFormatting sqref="A95:L95">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U32">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
-      <formula>"T"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A69:P69">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:P68">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
-      <formula>"T"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A95:L95">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+  <conditionalFormatting sqref="A33:XFD33">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73:L94">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+      <formula>"T"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37:P68">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+      <formula>"T"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:U32">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"T"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17930,7 +17923,7 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5" style="162" customWidth="1"/>
     <col min="2" max="2" width="14" style="162" customWidth="1"/>
@@ -17943,12 +17936,12 @@
     <col min="10" max="16384" width="9" style="161"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="176" t="s">
+    <row r="1" spans="1:21" customFormat="1" ht="82.5" customHeight="1">
+      <c r="A1" s="256" t="s">
         <v>426</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="178"/>
+      <c r="B1" s="257"/>
+      <c r="C1" s="258"/>
       <c r="D1" s="163"/>
       <c r="E1" s="163"/>
       <c r="F1" s="163"/>
@@ -17968,7 +17961,7 @@
       <c r="T1" s="163"/>
       <c r="U1" s="163"/>
     </row>
-    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="30" customHeight="1">
       <c r="A2" s="164" t="s">
         <v>321</v>
       </c>
@@ -17997,7 +17990,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="33">
       <c r="A3" s="165">
         <v>1</v>
       </c>
@@ -18024,7 +18017,7 @@
       </c>
       <c r="I3" s="167"/>
     </row>
-    <row r="4" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="33">
       <c r="A4" s="165">
         <v>2</v>
       </c>
@@ -18051,7 +18044,7 @@
       </c>
       <c r="I4" s="167"/>
     </row>
-    <row r="5" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="33">
       <c r="A5" s="165">
         <v>3</v>
       </c>
@@ -18078,7 +18071,7 @@
       </c>
       <c r="I5" s="167"/>
     </row>
-    <row r="6" spans="1:21" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="49.5">
       <c r="A6" s="165">
         <v>4</v>
       </c>
@@ -18105,7 +18098,7 @@
       </c>
       <c r="I6" s="167"/>
     </row>
-    <row r="7" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="33">
       <c r="A7" s="165">
         <v>5</v>
       </c>
@@ -18132,7 +18125,7 @@
       </c>
       <c r="I7" s="167"/>
     </row>
-    <row r="8" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="33">
       <c r="A8" s="165">
         <v>6</v>
       </c>
@@ -18159,7 +18152,7 @@
       </c>
       <c r="I8" s="167"/>
     </row>
-    <row r="9" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="33">
       <c r="A9" s="165">
         <v>7</v>
       </c>
@@ -18186,7 +18179,7 @@
       </c>
       <c r="I9" s="167"/>
     </row>
-    <row r="10" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="33">
       <c r="A10" s="165">
         <v>8</v>
       </c>
@@ -18213,7 +18206,7 @@
       </c>
       <c r="I10" s="167"/>
     </row>
-    <row r="11" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="33">
       <c r="A11" s="165">
         <v>9</v>
       </c>
@@ -18240,7 +18233,7 @@
       </c>
       <c r="I11" s="167"/>
     </row>
-    <row r="12" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="33">
       <c r="A12" s="165">
         <v>10</v>
       </c>
@@ -18267,7 +18260,7 @@
       </c>
       <c r="I12" s="167"/>
     </row>
-    <row r="13" spans="1:21" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="49.5">
       <c r="A13" s="165">
         <v>11</v>
       </c>
@@ -18294,7 +18287,7 @@
       </c>
       <c r="I13" s="167"/>
     </row>
-    <row r="14" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="33">
       <c r="A14" s="165">
         <v>12</v>
       </c>
@@ -18323,7 +18316,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="49.5">
       <c r="A15" s="174">
         <v>13</v>
       </c>
@@ -18352,7 +18345,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="33">
       <c r="A16" s="165">
         <v>14</v>
       </c>
@@ -18379,7 +18372,7 @@
       </c>
       <c r="I16" s="167"/>
     </row>
-    <row r="17" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="33">
       <c r="A17" s="165">
         <v>15</v>
       </c>
@@ -18406,7 +18399,7 @@
       </c>
       <c r="I17" s="167"/>
     </row>
-    <row r="18" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="33">
       <c r="A18" s="165">
         <v>16</v>
       </c>
@@ -18433,7 +18426,7 @@
       </c>
       <c r="I18" s="167"/>
     </row>
-    <row r="19" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="33">
       <c r="A19" s="165">
         <v>17</v>
       </c>
@@ -18460,7 +18453,7 @@
       </c>
       <c r="I19" s="167"/>
     </row>
-    <row r="20" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="33">
       <c r="A20" s="165">
         <v>18</v>
       </c>
@@ -18487,7 +18480,7 @@
       </c>
       <c r="I20" s="167"/>
     </row>
-    <row r="21" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="49.5">
       <c r="A21" s="174">
         <v>19</v>
       </c>
@@ -18516,7 +18509,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="49.5">
       <c r="A22" s="174">
         <v>20</v>
       </c>
@@ -18545,7 +18538,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="33">
       <c r="A23" s="165">
         <v>21</v>
       </c>
@@ -18572,7 +18565,7 @@
       </c>
       <c r="I23" s="167"/>
     </row>
-    <row r="24" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="33">
       <c r="A24" s="165">
         <v>22</v>
       </c>
@@ -18599,7 +18592,7 @@
       </c>
       <c r="I24" s="167"/>
     </row>
-    <row r="25" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="33">
       <c r="A25" s="165">
         <v>23</v>
       </c>
@@ -18626,7 +18619,7 @@
       </c>
       <c r="I25" s="167"/>
     </row>
-    <row r="26" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="33">
       <c r="A26" s="165">
         <v>24</v>
       </c>
@@ -18682,7 +18675,7 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="18.75" style="1" bestFit="1" customWidth="1"/>
@@ -18694,16 +18687,16 @@
     <col min="9" max="9" width="18.375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="254" t="s">
+    <row r="1" spans="1:12" ht="65.25" customHeight="1" thickBot="1">
+      <c r="A1" s="267" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="254"/>
-      <c r="C1" s="254"/>
-      <c r="D1" s="254"/>
-      <c r="E1" s="254"/>
-    </row>
-    <row r="2" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="267"/>
+      <c r="C1" s="267"/>
+      <c r="D1" s="267"/>
+      <c r="E1" s="267"/>
+    </row>
+    <row r="2" spans="1:12" ht="17.25" thickBot="1">
       <c r="A2" s="97" t="s">
         <v>104</v>
       </c>
@@ -18731,12 +18724,12 @@
       <c r="I2" s="99" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="246" t="s">
+      <c r="K2" s="259" t="s">
         <v>191</v>
       </c>
-      <c r="L2" s="247"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="260"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="90">
         <v>1</v>
       </c>
@@ -18763,17 +18756,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" s="90">
         <v>2</v>
       </c>
       <c r="B4" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="255">
+      <c r="C4" s="268">
         <v>2</v>
       </c>
-      <c r="D4" s="257" t="s">
+      <c r="D4" s="270" t="s">
         <v>112</v>
       </c>
       <c r="E4" s="91" t="s">
@@ -18788,15 +18781,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" s="90">
         <v>3</v>
       </c>
       <c r="B5" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="255"/>
-      <c r="D5" s="257"/>
+      <c r="C5" s="268"/>
+      <c r="D5" s="270"/>
       <c r="E5" s="91" t="s">
         <v>115</v>
       </c>
@@ -18809,15 +18802,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" s="90">
         <v>4</v>
       </c>
       <c r="B6" s="91" t="s">
         <v>217</v>
       </c>
-      <c r="C6" s="255"/>
-      <c r="D6" s="257"/>
+      <c r="C6" s="268"/>
+      <c r="D6" s="270"/>
       <c r="E6" s="91" t="s">
         <v>188</v>
       </c>
@@ -18834,15 +18827,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" s="90">
         <v>5</v>
       </c>
       <c r="B7" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="255"/>
-      <c r="D7" s="257"/>
+      <c r="C7" s="268"/>
+      <c r="D7" s="270"/>
       <c r="E7" s="91" t="s">
         <v>188</v>
       </c>
@@ -18859,17 +18852,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" s="90">
         <v>6</v>
       </c>
       <c r="B8" s="91" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="251">
+      <c r="C8" s="264">
         <v>3</v>
       </c>
-      <c r="D8" s="248" t="s">
+      <c r="D8" s="261" t="s">
         <v>112</v>
       </c>
       <c r="E8" s="91" t="s">
@@ -18884,15 +18877,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" s="90">
         <v>7</v>
       </c>
       <c r="B9" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="252"/>
-      <c r="D9" s="249"/>
+      <c r="C9" s="265"/>
+      <c r="D9" s="262"/>
       <c r="E9" s="91" t="s">
         <v>115</v>
       </c>
@@ -18905,15 +18898,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="27.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="27.75">
       <c r="A10" s="90">
         <v>8</v>
       </c>
       <c r="B10" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="252"/>
-      <c r="D10" s="249"/>
+      <c r="C10" s="265"/>
+      <c r="D10" s="262"/>
       <c r="E10" s="91" t="s">
         <v>188</v>
       </c>
@@ -18930,15 +18923,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="27.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="27.75">
       <c r="A11" s="90">
         <v>9</v>
       </c>
       <c r="B11" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="252"/>
-      <c r="D11" s="249"/>
+      <c r="C11" s="265"/>
+      <c r="D11" s="262"/>
       <c r="E11" s="91" t="s">
         <v>200</v>
       </c>
@@ -18955,15 +18948,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5">
       <c r="A12" s="90">
         <v>10</v>
       </c>
       <c r="B12" s="91" t="s">
         <v>433</v>
       </c>
-      <c r="C12" s="253"/>
-      <c r="D12" s="250"/>
+      <c r="C12" s="266"/>
+      <c r="D12" s="263"/>
       <c r="E12" s="91" t="s">
         <v>213</v>
       </c>
@@ -18980,17 +18973,17 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="A13" s="90">
         <v>11</v>
       </c>
       <c r="B13" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="268">
         <v>4</v>
       </c>
-      <c r="D13" s="257" t="s">
+      <c r="D13" s="270" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="91" t="s">
@@ -19007,15 +19000,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="A14" s="90">
         <v>12</v>
       </c>
       <c r="B14" s="91" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="255"/>
-      <c r="D14" s="257"/>
+      <c r="C14" s="268"/>
+      <c r="D14" s="270"/>
       <c r="E14" s="91" t="s">
         <v>115</v>
       </c>
@@ -19028,15 +19021,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="A15" s="90">
         <v>13</v>
       </c>
       <c r="B15" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="255"/>
-      <c r="D15" s="257"/>
+      <c r="C15" s="268"/>
+      <c r="D15" s="270"/>
       <c r="E15" s="91" t="s">
         <v>120</v>
       </c>
@@ -19049,15 +19042,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12">
       <c r="A16" s="90">
         <v>14</v>
       </c>
       <c r="B16" s="91" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="255"/>
-      <c r="D16" s="257"/>
+      <c r="C16" s="268"/>
+      <c r="D16" s="270"/>
       <c r="E16" s="91" t="s">
         <v>120</v>
       </c>
@@ -19070,15 +19063,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="90">
         <v>15</v>
       </c>
       <c r="B17" s="91" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="255"/>
-      <c r="D17" s="257"/>
+      <c r="C17" s="268"/>
+      <c r="D17" s="270"/>
       <c r="E17" s="91" t="s">
         <v>120</v>
       </c>
@@ -19091,17 +19084,17 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="90">
         <v>16</v>
       </c>
       <c r="B18" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="255">
+      <c r="C18" s="268">
         <v>5</v>
       </c>
-      <c r="D18" s="257" t="s">
+      <c r="D18" s="270" t="s">
         <v>113</v>
       </c>
       <c r="E18" s="91" t="s">
@@ -19118,15 +19111,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" s="90">
         <v>17</v>
       </c>
       <c r="B19" s="91" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="255"/>
-      <c r="D19" s="257"/>
+      <c r="C19" s="268"/>
+      <c r="D19" s="270"/>
       <c r="E19" s="91" t="s">
         <v>115</v>
       </c>
@@ -19139,15 +19132,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="90">
         <v>18</v>
       </c>
       <c r="B20" s="91" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="255"/>
-      <c r="D20" s="257"/>
+      <c r="C20" s="268"/>
+      <c r="D20" s="270"/>
       <c r="E20" s="91" t="s">
         <v>120</v>
       </c>
@@ -19160,15 +19153,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="90">
         <v>19</v>
       </c>
       <c r="B21" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="255"/>
-      <c r="D21" s="257"/>
+      <c r="C21" s="268"/>
+      <c r="D21" s="270"/>
       <c r="E21" s="91" t="s">
         <v>120</v>
       </c>
@@ -19181,15 +19174,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="90">
         <v>20</v>
       </c>
       <c r="B22" s="91" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="255"/>
-      <c r="D22" s="257"/>
+      <c r="C22" s="268"/>
+      <c r="D22" s="270"/>
       <c r="E22" s="91" t="s">
         <v>120</v>
       </c>
@@ -19202,17 +19195,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="90">
         <v>21</v>
       </c>
       <c r="B23" s="91" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="255">
+      <c r="C23" s="268">
         <v>6</v>
       </c>
-      <c r="D23" s="257" t="s">
+      <c r="D23" s="270" t="s">
         <v>113</v>
       </c>
       <c r="E23" s="91" t="s">
@@ -19229,15 +19222,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="90">
         <v>22</v>
       </c>
       <c r="B24" s="91" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="255"/>
-      <c r="D24" s="257"/>
+      <c r="C24" s="268"/>
+      <c r="D24" s="270"/>
       <c r="E24" s="91" t="s">
         <v>115</v>
       </c>
@@ -19250,15 +19243,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="90">
         <v>23</v>
       </c>
       <c r="B25" s="91" t="s">
         <v>179</v>
       </c>
-      <c r="C25" s="255"/>
-      <c r="D25" s="257"/>
+      <c r="C25" s="268"/>
+      <c r="D25" s="270"/>
       <c r="E25" s="91" t="s">
         <v>120</v>
       </c>
@@ -19271,15 +19264,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="90">
         <v>24</v>
       </c>
       <c r="B26" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="C26" s="255"/>
-      <c r="D26" s="257"/>
+      <c r="C26" s="268"/>
+      <c r="D26" s="270"/>
       <c r="E26" s="91" t="s">
         <v>120</v>
       </c>
@@ -19292,15 +19285,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="90">
         <v>25</v>
       </c>
       <c r="B27" s="91" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="255"/>
-      <c r="D27" s="257"/>
+      <c r="C27" s="268"/>
+      <c r="D27" s="270"/>
       <c r="E27" s="91" t="s">
         <v>120</v>
       </c>
@@ -19313,17 +19306,17 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="90">
         <v>26</v>
       </c>
       <c r="B28" s="91" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="255">
+      <c r="C28" s="268">
         <v>7</v>
       </c>
-      <c r="D28" s="257" t="s">
+      <c r="D28" s="270" t="s">
         <v>129</v>
       </c>
       <c r="E28" s="91" t="s">
@@ -19338,15 +19331,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="90">
         <v>27</v>
       </c>
       <c r="B29" s="91" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="255"/>
-      <c r="D29" s="257"/>
+      <c r="C29" s="268"/>
+      <c r="D29" s="270"/>
       <c r="E29" s="91" t="s">
         <v>120</v>
       </c>
@@ -19359,17 +19352,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="90">
         <v>28</v>
       </c>
       <c r="B30" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="255">
+      <c r="C30" s="268">
         <v>8</v>
       </c>
-      <c r="D30" s="257" t="s">
+      <c r="D30" s="270" t="s">
         <v>130</v>
       </c>
       <c r="E30" s="91" t="s">
@@ -19384,15 +19377,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="17.25" thickBot="1">
       <c r="A31" s="90">
         <v>29</v>
       </c>
       <c r="B31" s="95" t="s">
         <v>185</v>
       </c>
-      <c r="C31" s="256"/>
-      <c r="D31" s="258"/>
+      <c r="C31" s="269"/>
+      <c r="D31" s="271"/>
       <c r="E31" s="95" t="s">
         <v>120</v>
       </c>
@@ -19449,7 +19442,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="2" width="55.5" customWidth="1"/>
@@ -19457,57 +19450,57 @@
     <col min="6" max="6" width="40.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="188" t="s">
+    <row r="1" spans="1:6" ht="27.75" thickBot="1">
+      <c r="A1" s="250" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="190"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="251"/>
+      <c r="C1" s="252"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="139" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="269" t="s">
+      <c r="B2" s="272" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="270"/>
+      <c r="C2" s="273"/>
       <c r="D2" s="159" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="17.25" thickBot="1">
       <c r="A3" s="140" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="271" t="s">
+      <c r="B3" s="274" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="272"/>
+      <c r="C3" s="275"/>
       <c r="D3" s="160" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="140" t="s">
         <v>246</v>
       </c>
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="276" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="274"/>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="277"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1">
       <c r="A5" s="141" t="s">
         <v>245</v>
       </c>
-      <c r="B5" s="275" t="s">
+      <c r="B5" s="278" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="276"/>
-    </row>
-    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="279"/>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" thickBot="1"/>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1">
       <c r="A7" s="142" t="s">
         <v>239</v>
       </c>
@@ -19527,7 +19520,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="33">
       <c r="A8" s="145">
         <v>1</v>
       </c>
@@ -19543,7 +19536,7 @@
       <c r="E8" s="158"/>
       <c r="F8" s="148"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="149">
         <v>2</v>
       </c>
@@ -19559,7 +19552,7 @@
       <c r="E9" s="135"/>
       <c r="F9" s="150"/>
     </row>
-    <row r="10" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="49.5">
       <c r="A10" s="149">
         <v>3</v>
       </c>
@@ -19577,7 +19570,7 @@
       </c>
       <c r="F10" s="150"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="149">
         <v>4</v>
       </c>
@@ -19597,7 +19590,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="49.5">
       <c r="A12" s="149">
         <v>5</v>
       </c>
@@ -19615,7 +19608,7 @@
       </c>
       <c r="F12" s="150"/>
     </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="66">
       <c r="A13" s="149">
         <v>6</v>
       </c>
@@ -19631,7 +19624,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="61.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="61.5">
       <c r="A14" s="149">
         <v>7</v>
       </c>
@@ -19649,7 +19642,7 @@
       </c>
       <c r="F14" s="150"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="149">
         <v>8</v>
       </c>
@@ -19665,7 +19658,7 @@
       <c r="E15" s="135"/>
       <c r="F15" s="150"/>
     </row>
-    <row r="16" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="66">
       <c r="A16" s="149">
         <v>9</v>
       </c>
@@ -19679,7 +19672,7 @@
       <c r="E16" s="135"/>
       <c r="F16" s="150"/>
     </row>
-    <row r="17" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="49.5">
       <c r="A17" s="149">
         <v>10</v>
       </c>
@@ -19699,7 +19692,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="149">
         <v>11</v>
       </c>
@@ -19717,7 +19710,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="49.5">
       <c r="A19" s="149">
         <v>12</v>
       </c>
@@ -19733,7 +19726,7 @@
       <c r="E19" s="135"/>
       <c r="F19" s="150"/>
     </row>
-    <row r="20" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="33">
       <c r="A20" s="149">
         <v>13</v>
       </c>
@@ -19751,7 +19744,7 @@
       </c>
       <c r="F20" s="151"/>
     </row>
-    <row r="21" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="33">
       <c r="A21" s="149">
         <v>14</v>
       </c>
@@ -19769,7 +19762,7 @@
       </c>
       <c r="F21" s="151"/>
     </row>
-    <row r="22" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="33">
       <c r="A22" s="149">
         <v>15</v>
       </c>
@@ -19789,7 +19782,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="45">
       <c r="A23" s="149">
         <v>16</v>
       </c>
@@ -19807,7 +19800,7 @@
       </c>
       <c r="F23" s="150"/>
     </row>
-    <row r="24" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="45.75" thickBot="1">
       <c r="A24" s="153">
         <v>17</v>
       </c>
@@ -19855,20 +19848,20 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24" style="108" customWidth="1"/>
     <col min="2" max="2" width="86.875" customWidth="1"/>
     <col min="3" max="3" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="277" t="s">
+    <row r="1" spans="1:2" ht="42.75" customHeight="1">
+      <c r="A1" s="177" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="277"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" s="177"/>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="28" t="s">
         <v>161</v>
       </c>
@@ -19876,7 +19869,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="28" t="s">
         <v>144</v>
       </c>
@@ -19884,7 +19877,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="28" t="s">
         <v>151</v>
       </c>
@@ -19892,7 +19885,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="28" t="s">
         <v>152</v>
       </c>
@@ -19900,7 +19893,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="28" t="s">
         <v>145</v>
       </c>
@@ -19908,7 +19901,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="28" t="s">
         <v>146</v>
       </c>
@@ -19916,7 +19909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="82.5">
       <c r="A9" s="28" t="s">
         <v>147</v>
       </c>
@@ -19924,7 +19917,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="66">
       <c r="A10" s="28" t="s">
         <v>148</v>
       </c>
@@ -19932,7 +19925,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="28" t="s">
         <v>149</v>
       </c>
@@ -19940,7 +19933,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="28" t="s">
         <v>150</v>
       </c>
@@ -19948,13 +19941,13 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="28" t="s">
         <v>259</v>
       </c>
       <c r="B13" s="94"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="28" t="s">
         <v>161</v>
       </c>
@@ -19962,7 +19955,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" s="28" t="s">
         <v>144</v>
       </c>
@@ -19970,7 +19963,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" s="28" t="s">
         <v>151</v>
       </c>
@@ -19978,7 +19971,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="28" t="s">
         <v>152</v>
       </c>
@@ -19986,7 +19979,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="28" t="s">
         <v>145</v>
       </c>
@@ -19994,7 +19987,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" s="28" t="s">
         <v>146</v>
       </c>
@@ -20002,7 +19995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="115.5">
       <c r="A21" s="28" t="s">
         <v>147</v>
       </c>
@@ -20010,7 +20003,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" s="28" t="s">
         <v>148</v>
       </c>
@@ -20018,7 +20011,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" s="28" t="s">
         <v>149</v>
       </c>
@@ -20026,7 +20019,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" s="28" t="s">
         <v>150</v>
       </c>
@@ -20034,7 +20027,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="28" t="s">
         <v>259</v>
       </c>
@@ -20042,7 +20035,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" s="28" t="s">
         <v>161</v>
       </c>
@@ -20050,7 +20043,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" s="28" t="s">
         <v>144</v>
       </c>
@@ -20058,7 +20051,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" s="28" t="s">
         <v>151</v>
       </c>
@@ -20066,7 +20059,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" s="28" t="s">
         <v>152</v>
       </c>
@@ -20074,7 +20067,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" s="28" t="s">
         <v>145</v>
       </c>
@@ -20082,7 +20075,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" s="28" t="s">
         <v>146</v>
       </c>
@@ -20090,7 +20083,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="66">
       <c r="A33" s="28" t="s">
         <v>147</v>
       </c>
@@ -20098,7 +20091,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="33">
       <c r="A34" s="28" t="s">
         <v>148</v>
       </c>
@@ -20106,7 +20099,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" s="28" t="s">
         <v>149</v>
       </c>
@@ -20114,7 +20107,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" s="28" t="s">
         <v>150</v>
       </c>
@@ -20122,7 +20115,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" s="28" t="s">
         <v>259</v>
       </c>
@@ -20145,7 +20138,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D55356-662D-4938-A3FC-31FD24F9EB95}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA_TestCase_Portfolio.xlsx
+++ b/QA_TestCase_Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shell\OneDrive\Desktop\Dev\PJ\heoik93.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63D4FAC-AECA-420E-A381-37A3CD9EA187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A146E4D-AE58-487D-AFCD-D405FE67C6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="467">
   <si>
     <t>Edge</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3130,6 +3130,23 @@
 3. Caps Lock을 Off로 전환
 4. FieldID3을 클릭후, CapsLock을 On으로 전환</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4</t>
+  </si>
+  <si>
+    <t>#5</t>
+  </si>
+  <si>
+    <t>#6</t>
   </si>
 </sst>
 </file>
@@ -4617,316 +4634,316 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13268,20 +13285,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="178" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="S1" s="178" t="s">
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="S1" s="176" t="s">
         <v>229</v>
       </c>
-      <c r="T1" s="178"/>
-      <c r="U1" s="178"/>
-      <c r="V1" s="178"/>
+      <c r="T1" s="176"/>
+      <c r="U1" s="176"/>
+      <c r="V1" s="176"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="179" t="s">
         <v>436</v>
       </c>
       <c r="B2" s="31" t="s">
@@ -13305,7 +13322,7 @@
       </c>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="182"/>
+      <c r="A3" s="180"/>
       <c r="B3" s="30" t="s">
         <v>139</v>
       </c>
@@ -13326,7 +13343,7 @@
       <c r="V3" s="92"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="182"/>
+      <c r="A4" s="180"/>
       <c r="B4" s="2" t="s">
         <v>141</v>
       </c>
@@ -13347,7 +13364,7 @@
       <c r="V4" s="92"/>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="181" t="s">
         <v>438</v>
       </c>
       <c r="B5" s="31" t="s">
@@ -13370,7 +13387,7 @@
       <c r="V5" s="92"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="183"/>
+      <c r="A6" s="181"/>
       <c r="B6" s="30" t="s">
         <v>139</v>
       </c>
@@ -13391,7 +13408,7 @@
       <c r="V6" s="92"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="183"/>
+      <c r="A7" s="181"/>
       <c r="B7" s="2" t="s">
         <v>141</v>
       </c>
@@ -13412,7 +13429,7 @@
       <c r="V7" s="92"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="184" t="s">
+      <c r="A8" s="182" t="s">
         <v>233</v>
       </c>
       <c r="B8" s="31" t="s">
@@ -13435,7 +13452,7 @@
       <c r="V8" s="92"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="184"/>
+      <c r="A9" s="182"/>
       <c r="B9" s="30" t="s">
         <v>139</v>
       </c>
@@ -13456,7 +13473,7 @@
       <c r="V9" s="91"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="184"/>
+      <c r="A10" s="182"/>
       <c r="B10" s="2" t="s">
         <v>141</v>
       </c>
@@ -13477,7 +13494,7 @@
       <c r="V10" s="92"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="185" t="s">
+      <c r="A11" s="183" t="s">
         <v>439</v>
       </c>
       <c r="B11" s="31" t="s">
@@ -13500,7 +13517,7 @@
       <c r="V11" s="92"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="185"/>
+      <c r="A12" s="183"/>
       <c r="B12" s="30" t="s">
         <v>139</v>
       </c>
@@ -13521,7 +13538,7 @@
       <c r="V12" s="92"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="185"/>
+      <c r="A13" s="183"/>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
@@ -13542,7 +13559,7 @@
       <c r="V13" s="91"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="180" t="s">
+      <c r="A14" s="178" t="s">
         <v>140</v>
       </c>
       <c r="B14" s="27" t="s">
@@ -13565,7 +13582,7 @@
       <c r="V14" s="92"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="180"/>
+      <c r="A15" s="178"/>
       <c r="B15" s="29" t="s">
         <v>139</v>
       </c>
@@ -13586,7 +13603,7 @@
       <c r="V15" s="92"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="180"/>
+      <c r="A16" s="178"/>
       <c r="B16" s="28" t="s">
         <v>141</v>
       </c>
@@ -13659,10 +13676,10 @@
       <c r="V20" s="92"/>
     </row>
     <row r="21" spans="11:22">
-      <c r="K21" s="179" t="s">
+      <c r="K21" s="177" t="s">
         <v>237</v>
       </c>
-      <c r="L21" s="179"/>
+      <c r="L21" s="177"/>
       <c r="S21" s="132" t="s">
         <v>434</v>
       </c>
@@ -14029,7 +14046,7 @@
       <c r="S43" s="132" t="s">
         <v>437</v>
       </c>
-      <c r="T43" s="165" t="s">
+      <c r="T43" s="167" t="s">
         <v>331</v>
       </c>
       <c r="U43" s="92" t="str">
@@ -14042,7 +14059,7 @@
       <c r="S44" s="132" t="s">
         <v>437</v>
       </c>
-      <c r="T44" s="165" t="s">
+      <c r="T44" s="167" t="s">
         <v>428</v>
       </c>
       <c r="U44" s="92" t="str">
@@ -14055,7 +14072,7 @@
       <c r="S45" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T45" s="165" t="s">
+      <c r="T45" s="167" t="s">
         <v>340</v>
       </c>
       <c r="U45" s="92" t="str">
@@ -14068,7 +14085,7 @@
       <c r="S46" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T46" s="165" t="s">
+      <c r="T46" s="167" t="s">
         <v>345</v>
       </c>
       <c r="U46" s="92" t="str">
@@ -14081,7 +14098,7 @@
       <c r="S47" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T47" s="165" t="s">
+      <c r="T47" s="167" t="s">
         <v>350</v>
       </c>
       <c r="U47" s="92" t="str">
@@ -14094,7 +14111,7 @@
       <c r="S48" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T48" s="165" t="s">
+      <c r="T48" s="167" t="s">
         <v>354</v>
       </c>
       <c r="U48" s="92" t="str">
@@ -14107,7 +14124,7 @@
       <c r="S49" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T49" s="165" t="s">
+      <c r="T49" s="167" t="s">
         <v>357</v>
       </c>
       <c r="U49" s="92" t="str">
@@ -14120,7 +14137,7 @@
       <c r="S50" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T50" s="165" t="s">
+      <c r="T50" s="167" t="s">
         <v>361</v>
       </c>
       <c r="U50" s="92" t="str">
@@ -14133,7 +14150,7 @@
       <c r="S51" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T51" s="165" t="s">
+      <c r="T51" s="167" t="s">
         <v>365</v>
       </c>
       <c r="U51" s="92" t="str">
@@ -14146,7 +14163,7 @@
       <c r="S52" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T52" s="165" t="s">
+      <c r="T52" s="167" t="s">
         <v>368</v>
       </c>
       <c r="U52" s="92" t="str">
@@ -14159,7 +14176,7 @@
       <c r="S53" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T53" s="165" t="s">
+      <c r="T53" s="167" t="s">
         <v>371</v>
       </c>
       <c r="U53" s="92" t="str">
@@ -14172,7 +14189,7 @@
       <c r="S54" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T54" s="165" t="s">
+      <c r="T54" s="167" t="s">
         <v>376</v>
       </c>
       <c r="U54" s="92" t="str">
@@ -14185,7 +14202,7 @@
       <c r="S55" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T55" s="165" t="s">
+      <c r="T55" s="167" t="s">
         <v>382</v>
       </c>
       <c r="U55" s="92" t="str">
@@ -14198,7 +14215,7 @@
       <c r="S56" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T56" s="165" t="s">
+      <c r="T56" s="167" t="s">
         <v>385</v>
       </c>
       <c r="U56" s="92" t="str">
@@ -14211,7 +14228,7 @@
       <c r="S57" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T57" s="165" t="s">
+      <c r="T57" s="167" t="s">
         <v>389</v>
       </c>
       <c r="U57" s="92" t="str">
@@ -14224,7 +14241,7 @@
       <c r="S58" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T58" s="165" t="s">
+      <c r="T58" s="167" t="s">
         <v>393</v>
       </c>
       <c r="U58" s="92" t="str">
@@ -14237,7 +14254,7 @@
       <c r="S59" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T59" s="165" t="s">
+      <c r="T59" s="167" t="s">
         <v>397</v>
       </c>
       <c r="U59" s="92" t="str">
@@ -14250,7 +14267,7 @@
       <c r="S60" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T60" s="165" t="s">
+      <c r="T60" s="167" t="s">
         <v>400</v>
       </c>
       <c r="U60" s="92" t="str">
@@ -14263,7 +14280,7 @@
       <c r="S61" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T61" s="165" t="s">
+      <c r="T61" s="167" t="s">
         <v>404</v>
       </c>
       <c r="U61" s="92" t="str">
@@ -14276,20 +14293,22 @@
       <c r="S62" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T62" s="165" t="s">
+      <c r="T62" s="167" t="s">
         <v>408</v>
       </c>
       <c r="U62" s="92" t="str">
         <f>VLOOKUP(T62,'CheckList Case'!C22:H45,6,FALSE)</f>
         <v>Fail</v>
       </c>
-      <c r="V62" s="92"/>
+      <c r="V62" s="91" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="63" spans="19:22">
       <c r="S63" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T63" s="176" t="s">
+      <c r="T63" s="279" t="s">
         <v>410</v>
       </c>
       <c r="U63" s="92" t="str">
@@ -14302,7 +14321,7 @@
       <c r="S64" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T64" s="176" t="s">
+      <c r="T64" s="279" t="s">
         <v>414</v>
       </c>
       <c r="U64" s="92" t="str">
@@ -14315,7 +14334,7 @@
       <c r="S65" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T65" s="176" t="s">
+      <c r="T65" s="279" t="s">
         <v>418</v>
       </c>
       <c r="U65" s="92" t="str">
@@ -14328,7 +14347,7 @@
       <c r="S66" s="133" t="s">
         <v>435</v>
       </c>
-      <c r="T66" s="176" t="s">
+      <c r="T66" s="279" t="s">
         <v>422</v>
       </c>
       <c r="U66" s="92" t="str">
@@ -14465,7 +14484,9 @@
         <f>VLOOKUP(T76,'FieldRule Case'!$B$3:$I$31,8,FALSE)</f>
         <v>Fail</v>
       </c>
-      <c r="V76" s="92"/>
+      <c r="V76" s="91" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="77" spans="19:22">
       <c r="S77" s="132" t="s">
@@ -14728,7 +14749,6 @@
       <c r="V96" s="92"/>
     </row>
   </sheetData>
-  <autoFilter ref="S2:V2" xr:uid="{43C3CD3D-F5F5-4E8E-96B0-CB9235DE1118}"/>
   <mergeCells count="8">
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="K21:L21"/>
@@ -14767,11 +14787,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="87.75" thickBot="1">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="186" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="252"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="188"/>
       <c r="D1" s="6" t="s">
         <v>17</v>
       </c>
@@ -14828,10 +14848,10 @@
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="236" t="s">
+      <c r="A2" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="209" t="s">
+      <c r="B2" s="203" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -14873,8 +14893,8 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="237"/>
-      <c r="B3" s="182"/>
+      <c r="A3" s="201"/>
+      <c r="B3" s="180"/>
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -14912,8 +14932,8 @@
       <c r="U3" s="17"/>
     </row>
     <row r="4" spans="1:21" ht="17.25" thickBot="1">
-      <c r="A4" s="238"/>
-      <c r="B4" s="210"/>
+      <c r="A4" s="202"/>
+      <c r="B4" s="204"/>
       <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
@@ -14943,7 +14963,7 @@
       <c r="U4" s="18"/>
     </row>
     <row r="5" spans="1:21" ht="16.5" customHeight="1">
-      <c r="A5" s="233" t="s">
+      <c r="A5" s="197" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="48" t="s">
@@ -14978,8 +14998,8 @@
       <c r="U5" s="19"/>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="234"/>
-      <c r="B6" s="183" t="s">
+      <c r="A6" s="198"/>
+      <c r="B6" s="181" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -15007,8 +15027,8 @@
       <c r="U6" s="17"/>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="234"/>
-      <c r="B7" s="183"/>
+      <c r="A7" s="198"/>
+      <c r="B7" s="181"/>
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
@@ -15034,8 +15054,8 @@
       <c r="U7" s="17"/>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="234"/>
-      <c r="B8" s="183" t="s">
+      <c r="A8" s="198"/>
+      <c r="B8" s="181" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -15063,8 +15083,8 @@
       <c r="U8" s="17"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="234"/>
-      <c r="B9" s="183"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="181"/>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
@@ -15090,8 +15110,8 @@
       <c r="U9" s="17"/>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="234"/>
-      <c r="B10" s="183" t="s">
+      <c r="A10" s="198"/>
+      <c r="B10" s="181" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -15121,8 +15141,8 @@
       <c r="U10" s="17"/>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="234"/>
-      <c r="B11" s="183"/>
+      <c r="A11" s="198"/>
+      <c r="B11" s="181"/>
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
@@ -15148,7 +15168,7 @@
       <c r="U11" s="17"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="234"/>
+      <c r="A12" s="198"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -15177,7 +15197,7 @@
       <c r="U12" s="17"/>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="234"/>
+      <c r="A13" s="198"/>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
@@ -15206,7 +15226,7 @@
       <c r="U13" s="17"/>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="234"/>
+      <c r="A14" s="198"/>
       <c r="B14" s="2" t="s">
         <v>4</v>
       </c>
@@ -15235,7 +15255,7 @@
       <c r="U14" s="17"/>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="234"/>
+      <c r="A15" s="198"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -15266,7 +15286,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="234"/>
+      <c r="A16" s="198"/>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
@@ -15295,7 +15315,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:22" ht="33.75" thickBot="1">
-      <c r="A17" s="235"/>
+      <c r="A17" s="199"/>
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
@@ -15326,13 +15346,13 @@
       <c r="U17" s="20"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="230" t="s">
+      <c r="A18" s="194" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="253" t="s">
+      <c r="B18" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="253"/>
+      <c r="C18" s="189"/>
       <c r="D18" s="16" t="s">
         <v>102</v>
       </c>
@@ -15389,11 +15409,11 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="32.25" customHeight="1">
-      <c r="A19" s="231"/>
-      <c r="B19" s="254" t="s">
+      <c r="A19" s="195"/>
+      <c r="B19" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="254"/>
+      <c r="C19" s="190"/>
       <c r="D19" s="17" t="s">
         <v>102</v>
       </c>
@@ -15446,11 +15466,11 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A20" s="232"/>
-      <c r="B20" s="255" t="s">
+      <c r="A20" s="196"/>
+      <c r="B20" s="191" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="255"/>
+      <c r="C20" s="191"/>
       <c r="D20" s="18" t="s">
         <v>102</v>
       </c>
@@ -15503,7 +15523,7 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="241" t="s">
+      <c r="A21" s="207" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="46" t="s">
@@ -15546,7 +15566,7 @@
       <c r="U21" s="19"/>
     </row>
     <row r="22" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A22" s="242"/>
+      <c r="A22" s="208"/>
       <c r="B22" s="45" t="s">
         <v>21</v>
       </c>
@@ -15591,13 +15611,13 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="17.25" thickTop="1">
-      <c r="A23" s="245" t="s">
+      <c r="A23" s="213" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="246" t="s">
+      <c r="B23" s="214" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="246"/>
+      <c r="C23" s="214"/>
       <c r="D23" s="21" t="s">
         <v>102</v>
       </c>
@@ -15642,11 +15662,11 @@
       <c r="U23" s="21"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="234"/>
-      <c r="B24" s="183" t="s">
+      <c r="A24" s="198"/>
+      <c r="B24" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="183"/>
+      <c r="C24" s="181"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
@@ -15671,11 +15691,11 @@
       <c r="U24" s="17"/>
     </row>
     <row r="25" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A25" s="235"/>
-      <c r="B25" s="247" t="s">
+      <c r="A25" s="199"/>
+      <c r="B25" s="215" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="247"/>
+      <c r="C25" s="215"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
@@ -15700,13 +15720,13 @@
       </c>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="230" t="s">
+      <c r="A26" s="194" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="192" t="s">
+      <c r="B26" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="192"/>
+      <c r="C26" s="209"/>
       <c r="D26" s="16" t="s">
         <v>102</v>
       </c>
@@ -15759,11 +15779,11 @@
       </c>
     </row>
     <row r="27" spans="1:22">
-      <c r="A27" s="244"/>
-      <c r="B27" s="248" t="s">
+      <c r="A27" s="212"/>
+      <c r="B27" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="249"/>
+      <c r="C27" s="185"/>
       <c r="D27" s="24" t="s">
         <v>56</v>
       </c>
@@ -15817,11 +15837,11 @@
       <c r="V27" s="26"/>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="244"/>
-      <c r="B28" s="248" t="s">
+      <c r="A28" s="212"/>
+      <c r="B28" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="185"/>
       <c r="D28" s="17" t="s">
         <v>102</v>
       </c>
@@ -15874,8 +15894,8 @@
       </c>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="231"/>
-      <c r="B29" s="239" t="s">
+      <c r="A29" s="195"/>
+      <c r="B29" s="205" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="14" t="s">
@@ -15925,8 +15945,8 @@
       <c r="U29" s="22"/>
     </row>
     <row r="30" spans="1:22" ht="33">
-      <c r="A30" s="231"/>
-      <c r="B30" s="240"/>
+      <c r="A30" s="195"/>
+      <c r="B30" s="206"/>
       <c r="C30" s="15" t="s">
         <v>53</v>
       </c>
@@ -15974,11 +15994,11 @@
       <c r="U30" s="22"/>
     </row>
     <row r="31" spans="1:22">
-      <c r="A31" s="231"/>
-      <c r="B31" s="198" t="s">
+      <c r="A31" s="195"/>
+      <c r="B31" s="210" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="198"/>
+      <c r="C31" s="210"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -16003,11 +16023,11 @@
       <c r="U31" s="17"/>
     </row>
     <row r="32" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A32" s="232"/>
-      <c r="B32" s="243" t="s">
+      <c r="A32" s="196"/>
+      <c r="B32" s="211" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="243"/>
+      <c r="C32" s="211"/>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
       <c r="F32" s="23"/>
@@ -16032,11 +16052,11 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="33" customHeight="1" thickBot="1">
-      <c r="A33" s="187" t="s">
+      <c r="A33" s="192" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="188"/>
-      <c r="C33" s="188"/>
+      <c r="B33" s="193"/>
+      <c r="C33" s="193"/>
       <c r="D33" s="102" t="s">
         <v>136</v>
       </c>
@@ -16094,11 +16114,11 @@
     </row>
     <row r="35" spans="1:21" ht="17.25" thickBot="1"/>
     <row r="36" spans="1:21" ht="87" thickBot="1">
-      <c r="A36" s="221" t="s">
+      <c r="A36" s="216" t="s">
         <v>431</v>
       </c>
-      <c r="B36" s="222"/>
-      <c r="C36" s="223"/>
+      <c r="B36" s="217"/>
+      <c r="C36" s="218"/>
       <c r="D36" s="54" t="s">
         <v>59</v>
       </c>
@@ -16140,10 +16160,10 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="18">
-      <c r="A37" s="224" t="s">
+      <c r="A37" s="219" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="209" t="s">
+      <c r="B37" s="203" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -16172,8 +16192,8 @@
       <c r="P37" s="55"/>
     </row>
     <row r="38" spans="1:21" ht="18">
-      <c r="A38" s="225"/>
-      <c r="B38" s="182"/>
+      <c r="A38" s="220"/>
+      <c r="B38" s="180"/>
       <c r="C38" s="5" t="s">
         <v>1</v>
       </c>
@@ -16206,8 +16226,8 @@
       </c>
     </row>
     <row r="39" spans="1:21" ht="17.25" thickBot="1">
-      <c r="A39" s="226"/>
-      <c r="B39" s="210"/>
+      <c r="A39" s="221"/>
+      <c r="B39" s="204"/>
       <c r="C39" s="9" t="s">
         <v>2</v>
       </c>
@@ -16230,7 +16250,7 @@
       <c r="P39" s="56"/>
     </row>
     <row r="40" spans="1:21">
-      <c r="A40" s="227" t="s">
+      <c r="A40" s="222" t="s">
         <v>31</v>
       </c>
       <c r="B40" s="48" t="s">
@@ -16258,8 +16278,8 @@
       <c r="P40" s="57"/>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="228"/>
-      <c r="B41" s="183" t="s">
+      <c r="A41" s="223"/>
+      <c r="B41" s="181" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -16282,8 +16302,8 @@
       <c r="P41" s="52"/>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="228"/>
-      <c r="B42" s="183"/>
+      <c r="A42" s="223"/>
+      <c r="B42" s="181"/>
       <c r="C42" s="3" t="s">
         <v>11</v>
       </c>
@@ -16304,8 +16324,8 @@
       <c r="P42" s="52"/>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="228"/>
-      <c r="B43" s="183" t="s">
+      <c r="A43" s="223"/>
+      <c r="B43" s="181" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -16328,8 +16348,8 @@
       <c r="P43" s="52"/>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="228"/>
-      <c r="B44" s="183"/>
+      <c r="A44" s="223"/>
+      <c r="B44" s="181"/>
       <c r="C44" s="3" t="s">
         <v>11</v>
       </c>
@@ -16350,8 +16370,8 @@
       <c r="P44" s="52"/>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="228"/>
-      <c r="B45" s="183" t="s">
+      <c r="A45" s="223"/>
+      <c r="B45" s="181" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -16374,8 +16394,8 @@
       <c r="P45" s="52"/>
     </row>
     <row r="46" spans="1:21">
-      <c r="A46" s="228"/>
-      <c r="B46" s="183"/>
+      <c r="A46" s="223"/>
+      <c r="B46" s="181"/>
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
@@ -16396,7 +16416,7 @@
       <c r="P46" s="52"/>
     </row>
     <row r="47" spans="1:21">
-      <c r="A47" s="228"/>
+      <c r="A47" s="223"/>
       <c r="B47" s="2" t="s">
         <v>4</v>
       </c>
@@ -16420,7 +16440,7 @@
       <c r="P47" s="52"/>
     </row>
     <row r="48" spans="1:21">
-      <c r="A48" s="228"/>
+      <c r="A48" s="223"/>
       <c r="B48" s="2" t="s">
         <v>6</v>
       </c>
@@ -16444,7 +16464,7 @@
       <c r="P48" s="52"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="228"/>
+      <c r="A49" s="223"/>
       <c r="B49" s="2" t="s">
         <v>7</v>
       </c>
@@ -16468,7 +16488,7 @@
       <c r="P49" s="52"/>
     </row>
     <row r="50" spans="1:16" ht="33.75" thickBot="1">
-      <c r="A50" s="229"/>
+      <c r="A50" s="224"/>
       <c r="B50" s="10" t="s">
         <v>15</v>
       </c>
@@ -16497,10 +16517,10 @@
       <c r="A51" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="214" t="s">
+      <c r="B51" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="214"/>
+      <c r="C51" s="225"/>
       <c r="D51" s="64" t="s">
         <v>102</v>
       </c>
@@ -16542,10 +16562,10 @@
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="206" t="s">
+      <c r="A52" s="226" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="215" t="s">
+      <c r="B52" s="229" t="s">
         <v>22</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -16570,8 +16590,8 @@
       <c r="P52" s="55"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="207"/>
-      <c r="B53" s="216"/>
+      <c r="A53" s="227"/>
+      <c r="B53" s="230"/>
       <c r="C53" s="12" t="s">
         <v>75</v>
       </c>
@@ -16594,8 +16614,8 @@
       <c r="P53" s="57"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="207"/>
-      <c r="B54" s="216"/>
+      <c r="A54" s="227"/>
+      <c r="B54" s="230"/>
       <c r="C54" s="12" t="s">
         <v>73</v>
       </c>
@@ -16618,8 +16638,8 @@
       <c r="P54" s="57"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="207"/>
-      <c r="B55" s="217"/>
+      <c r="A55" s="227"/>
+      <c r="B55" s="231"/>
       <c r="C55" s="12" t="s">
         <v>74</v>
       </c>
@@ -16642,8 +16662,8 @@
       <c r="P55" s="57"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="207"/>
-      <c r="B56" s="218" t="s">
+      <c r="A56" s="227"/>
+      <c r="B56" s="232" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="12" t="s">
@@ -16668,8 +16688,8 @@
       <c r="P56" s="57"/>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="207"/>
-      <c r="B57" s="216"/>
+      <c r="A57" s="227"/>
+      <c r="B57" s="230"/>
       <c r="C57" s="12" t="s">
         <v>72</v>
       </c>
@@ -16692,8 +16712,8 @@
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="207"/>
-      <c r="B58" s="216"/>
+      <c r="A58" s="227"/>
+      <c r="B58" s="230"/>
       <c r="C58" s="12" t="s">
         <v>73</v>
       </c>
@@ -16716,8 +16736,8 @@
       </c>
     </row>
     <row r="59" spans="1:16" ht="17.25" thickBot="1">
-      <c r="A59" s="208"/>
-      <c r="B59" s="219"/>
+      <c r="A59" s="228"/>
+      <c r="B59" s="233"/>
       <c r="C59" s="68" t="s">
         <v>74</v>
       </c>
@@ -16743,10 +16763,10 @@
       <c r="A60" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="220" t="s">
+      <c r="B60" s="234" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="220"/>
+      <c r="C60" s="234"/>
       <c r="D60" s="19" t="s">
         <v>102</v>
       </c>
@@ -16788,13 +16808,13 @@
       </c>
     </row>
     <row r="61" spans="1:16" ht="18">
-      <c r="A61" s="190" t="s">
+      <c r="A61" s="235" t="s">
         <v>18</v>
       </c>
-      <c r="B61" s="192" t="s">
+      <c r="B61" s="209" t="s">
         <v>76</v>
       </c>
-      <c r="C61" s="192"/>
+      <c r="C61" s="209"/>
       <c r="D61" s="73" t="s">
         <v>102</v>
       </c>
@@ -16836,7 +16856,7 @@
       </c>
     </row>
     <row r="62" spans="1:16" ht="66.75" thickBot="1">
-      <c r="A62" s="211"/>
+      <c r="A62" s="236"/>
       <c r="B62" s="4" t="s">
         <v>77</v>
       </c>
@@ -16887,10 +16907,10 @@
       <c r="A63" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B63" s="189" t="s">
+      <c r="B63" s="237" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="189"/>
+      <c r="C63" s="237"/>
       <c r="D63" s="49" t="s">
         <v>102</v>
       </c>
@@ -16932,13 +16952,13 @@
       </c>
     </row>
     <row r="64" spans="1:16" ht="18">
-      <c r="A64" s="190" t="s">
+      <c r="A64" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="192" t="s">
+      <c r="B64" s="209" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="192"/>
+      <c r="C64" s="209"/>
       <c r="D64" s="73" t="s">
         <v>102</v>
       </c>
@@ -16980,8 +17000,8 @@
       </c>
     </row>
     <row r="65" spans="1:16" ht="49.5">
-      <c r="A65" s="196"/>
-      <c r="B65" s="212" t="s">
+      <c r="A65" s="238"/>
+      <c r="B65" s="240" t="s">
         <v>83</v>
       </c>
       <c r="C65" s="15" t="s">
@@ -17020,8 +17040,8 @@
       <c r="P65" s="52"/>
     </row>
     <row r="66" spans="1:16" ht="50.25" thickBot="1">
-      <c r="A66" s="191"/>
-      <c r="B66" s="213"/>
+      <c r="A66" s="239"/>
+      <c r="B66" s="241"/>
       <c r="C66" s="53" t="s">
         <v>82</v>
       </c>
@@ -17051,10 +17071,10 @@
       <c r="A67" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B67" s="195" t="s">
+      <c r="B67" s="242" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="195"/>
+      <c r="C67" s="242"/>
       <c r="D67" s="79" t="s">
         <v>102</v>
       </c>
@@ -17087,10 +17107,10 @@
       <c r="A68" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="186" t="s">
+      <c r="B68" s="243" t="s">
         <v>88</v>
       </c>
-      <c r="C68" s="186"/>
+      <c r="C68" s="243"/>
       <c r="D68" s="80" t="s">
         <v>102</v>
       </c>
@@ -17120,11 +17140,11 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="17.25" thickBot="1">
-      <c r="A69" s="187" t="s">
+      <c r="A69" s="192" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="188"/>
-      <c r="C69" s="188"/>
+      <c r="B69" s="193"/>
+      <c r="C69" s="193"/>
       <c r="D69" s="102" t="s">
         <v>137</v>
       </c>
@@ -17167,11 +17187,11 @@
     </row>
     <row r="71" spans="1:16" ht="17.25" thickBot="1"/>
     <row r="72" spans="1:16" ht="78" thickBot="1">
-      <c r="A72" s="203" t="s">
+      <c r="A72" s="244" t="s">
         <v>430</v>
       </c>
-      <c r="B72" s="204"/>
-      <c r="C72" s="205"/>
+      <c r="B72" s="245"/>
+      <c r="C72" s="246"/>
       <c r="D72" s="54" t="s">
         <v>90</v>
       </c>
@@ -17201,10 +17221,10 @@
       </c>
     </row>
     <row r="73" spans="1:16">
-      <c r="A73" s="206" t="s">
+      <c r="A73" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="209" t="s">
+      <c r="B73" s="203" t="s">
         <v>3</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -17227,8 +17247,8 @@
       <c r="L73" s="112"/>
     </row>
     <row r="74" spans="1:16">
-      <c r="A74" s="207"/>
-      <c r="B74" s="182"/>
+      <c r="A74" s="227"/>
+      <c r="B74" s="180"/>
       <c r="C74" s="5" t="s">
         <v>1</v>
       </c>
@@ -17249,8 +17269,8 @@
       <c r="L74" s="113"/>
     </row>
     <row r="75" spans="1:16" ht="17.25" thickBot="1">
-      <c r="A75" s="207"/>
-      <c r="B75" s="210"/>
+      <c r="A75" s="227"/>
+      <c r="B75" s="204"/>
       <c r="C75" s="9" t="s">
         <v>2</v>
       </c>
@@ -17271,7 +17291,7 @@
       </c>
     </row>
     <row r="76" spans="1:16">
-      <c r="A76" s="207"/>
+      <c r="A76" s="227"/>
       <c r="B76" s="46" t="s">
         <v>14</v>
       </c>
@@ -17295,8 +17315,8 @@
       <c r="L76" s="115"/>
     </row>
     <row r="77" spans="1:16">
-      <c r="A77" s="207"/>
-      <c r="B77" s="182" t="s">
+      <c r="A77" s="227"/>
+      <c r="B77" s="180" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="5" t="s">
@@ -17317,8 +17337,8 @@
       <c r="L77" s="113"/>
     </row>
     <row r="78" spans="1:16">
-      <c r="A78" s="207"/>
-      <c r="B78" s="182"/>
+      <c r="A78" s="227"/>
+      <c r="B78" s="180"/>
       <c r="C78" s="5" t="s">
         <v>11</v>
       </c>
@@ -17337,7 +17357,7 @@
       </c>
     </row>
     <row r="79" spans="1:16" ht="33.75" thickBot="1">
-      <c r="A79" s="208"/>
+      <c r="A79" s="228"/>
       <c r="B79" s="45" t="s">
         <v>15</v>
       </c>
@@ -17359,7 +17379,7 @@
       <c r="L79" s="116"/>
     </row>
     <row r="80" spans="1:16">
-      <c r="A80" s="199" t="s">
+      <c r="A80" s="247" t="s">
         <v>99</v>
       </c>
       <c r="B80" s="88" t="s">
@@ -17397,11 +17417,11 @@
       </c>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="200"/>
-      <c r="B81" s="183" t="s">
+      <c r="A81" s="248"/>
+      <c r="B81" s="181" t="s">
         <v>212</v>
       </c>
-      <c r="C81" s="183"/>
+      <c r="C81" s="181"/>
       <c r="D81" s="113" t="s">
         <v>226</v>
       </c>
@@ -17419,11 +17439,11 @@
       <c r="L81" s="113"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="200"/>
-      <c r="B82" s="183" t="s">
+      <c r="A82" s="248"/>
+      <c r="B82" s="181" t="s">
         <v>209</v>
       </c>
-      <c r="C82" s="183"/>
+      <c r="C82" s="181"/>
       <c r="D82" s="113"/>
       <c r="E82" s="113" t="s">
         <v>226</v>
@@ -17441,11 +17461,11 @@
       <c r="L82" s="113"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="200"/>
-      <c r="B83" s="183" t="s">
+      <c r="A83" s="248"/>
+      <c r="B83" s="181" t="s">
         <v>211</v>
       </c>
-      <c r="C83" s="183"/>
+      <c r="C83" s="181"/>
       <c r="D83" s="113"/>
       <c r="E83" s="113"/>
       <c r="F83" s="113" t="s">
@@ -17463,11 +17483,11 @@
       </c>
     </row>
     <row r="84" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A84" s="201"/>
-      <c r="B84" s="202" t="s">
+      <c r="A84" s="249"/>
+      <c r="B84" s="250" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="202"/>
+      <c r="C84" s="250"/>
       <c r="D84" s="114" t="s">
         <v>226</v>
       </c>
@@ -17497,13 +17517,13 @@
       </c>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="196" t="s">
+      <c r="A85" s="238" t="s">
         <v>19</v>
       </c>
-      <c r="B85" s="197" t="s">
+      <c r="B85" s="251" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="198"/>
+      <c r="C85" s="210"/>
       <c r="D85" s="117" t="s">
         <v>56</v>
       </c>
@@ -17533,7 +17553,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" ht="83.25" thickBot="1">
-      <c r="A86" s="191"/>
+      <c r="A86" s="239"/>
       <c r="B86" s="111" t="s">
         <v>77</v>
       </c>
@@ -17572,10 +17592,10 @@
       <c r="A87" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B87" s="189" t="s">
+      <c r="B87" s="237" t="s">
         <v>222</v>
       </c>
-      <c r="C87" s="189"/>
+      <c r="C87" s="237"/>
       <c r="D87" s="121"/>
       <c r="E87" s="122" t="s">
         <v>226</v>
@@ -17599,13 +17619,13 @@
       </c>
     </row>
     <row r="88" spans="1:12">
-      <c r="A88" s="190" t="s">
+      <c r="A88" s="235" t="s">
         <v>18</v>
       </c>
-      <c r="B88" s="192" t="s">
+      <c r="B88" s="209" t="s">
         <v>223</v>
       </c>
-      <c r="C88" s="192"/>
+      <c r="C88" s="209"/>
       <c r="D88" s="123"/>
       <c r="E88" s="124" t="s">
         <v>226</v>
@@ -17623,7 +17643,7 @@
       <c r="L88" s="124"/>
     </row>
     <row r="89" spans="1:12" ht="99.75" thickBot="1">
-      <c r="A89" s="191"/>
+      <c r="A89" s="239"/>
       <c r="B89" s="4" t="s">
         <v>77</v>
       </c>
@@ -17650,10 +17670,10 @@
       <c r="A90" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B90" s="189" t="s">
+      <c r="B90" s="237" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="189"/>
+      <c r="C90" s="237"/>
       <c r="D90" s="121"/>
       <c r="E90" s="121"/>
       <c r="F90" s="122" t="s">
@@ -17671,13 +17691,13 @@
       </c>
     </row>
     <row r="91" spans="1:12">
-      <c r="A91" s="190" t="s">
+      <c r="A91" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="B91" s="192" t="s">
+      <c r="B91" s="209" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="192"/>
+      <c r="C91" s="209"/>
       <c r="D91" s="123"/>
       <c r="E91" s="123"/>
       <c r="F91" s="124" t="s">
@@ -17695,11 +17715,11 @@
       </c>
     </row>
     <row r="92" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A92" s="191"/>
-      <c r="B92" s="193" t="s">
+      <c r="A92" s="239"/>
+      <c r="B92" s="252" t="s">
         <v>82</v>
       </c>
-      <c r="C92" s="194"/>
+      <c r="C92" s="253"/>
       <c r="D92" s="126"/>
       <c r="E92" s="126"/>
       <c r="F92" s="114" t="s">
@@ -17720,10 +17740,10 @@
       <c r="A93" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B93" s="195" t="s">
+      <c r="B93" s="242" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="195"/>
+      <c r="C93" s="242"/>
       <c r="D93" s="127"/>
       <c r="E93" s="127"/>
       <c r="F93" s="128" t="s">
@@ -17744,10 +17764,10 @@
       <c r="A94" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="B94" s="186" t="s">
+      <c r="B94" s="243" t="s">
         <v>228</v>
       </c>
-      <c r="C94" s="186"/>
+      <c r="C94" s="243"/>
       <c r="D94" s="129"/>
       <c r="E94" s="129"/>
       <c r="F94" s="130" t="s">
@@ -17765,11 +17785,11 @@
       </c>
     </row>
     <row r="95" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A95" s="187" t="s">
+      <c r="A95" s="192" t="s">
         <v>138</v>
       </c>
-      <c r="B95" s="188"/>
-      <c r="C95" s="188"/>
+      <c r="B95" s="193"/>
+      <c r="C95" s="193"/>
       <c r="D95" s="102" t="s">
         <v>136</v>
       </c>
@@ -17800,14 +17820,48 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="A40:A50"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A5:A17"/>
@@ -17824,48 +17878,14 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="A40:A50"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A95:L95">
@@ -17937,11 +17957,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customFormat="1" ht="82.5" customHeight="1">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="254" t="s">
         <v>426</v>
       </c>
-      <c r="B1" s="257"/>
-      <c r="C1" s="258"/>
+      <c r="B1" s="255"/>
+      <c r="C1" s="256"/>
       <c r="D1" s="163"/>
       <c r="E1" s="163"/>
       <c r="F1" s="163"/>
@@ -18688,13 +18708,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="65.25" customHeight="1" thickBot="1">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="265" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="267"/>
-      <c r="C1" s="267"/>
-      <c r="D1" s="267"/>
-      <c r="E1" s="267"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
     </row>
     <row r="2" spans="1:12" ht="17.25" thickBot="1">
       <c r="A2" s="97" t="s">
@@ -18724,10 +18744,10 @@
       <c r="I2" s="99" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="259" t="s">
+      <c r="K2" s="257" t="s">
         <v>191</v>
       </c>
-      <c r="L2" s="260"/>
+      <c r="L2" s="258"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="90">
@@ -18763,10 +18783,10 @@
       <c r="B4" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="268">
+      <c r="C4" s="266">
         <v>2</v>
       </c>
-      <c r="D4" s="270" t="s">
+      <c r="D4" s="268" t="s">
         <v>112</v>
       </c>
       <c r="E4" s="91" t="s">
@@ -18788,8 +18808,8 @@
       <c r="B5" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="268"/>
-      <c r="D5" s="270"/>
+      <c r="C5" s="266"/>
+      <c r="D5" s="268"/>
       <c r="E5" s="91" t="s">
         <v>115</v>
       </c>
@@ -18809,8 +18829,8 @@
       <c r="B6" s="91" t="s">
         <v>217</v>
       </c>
-      <c r="C6" s="268"/>
-      <c r="D6" s="270"/>
+      <c r="C6" s="266"/>
+      <c r="D6" s="268"/>
       <c r="E6" s="91" t="s">
         <v>188</v>
       </c>
@@ -18834,8 +18854,8 @@
       <c r="B7" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="268"/>
-      <c r="D7" s="270"/>
+      <c r="C7" s="266"/>
+      <c r="D7" s="268"/>
       <c r="E7" s="91" t="s">
         <v>188</v>
       </c>
@@ -18859,10 +18879,10 @@
       <c r="B8" s="91" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="264">
+      <c r="C8" s="262">
         <v>3</v>
       </c>
-      <c r="D8" s="261" t="s">
+      <c r="D8" s="259" t="s">
         <v>112</v>
       </c>
       <c r="E8" s="91" t="s">
@@ -18884,8 +18904,8 @@
       <c r="B9" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="265"/>
-      <c r="D9" s="262"/>
+      <c r="C9" s="263"/>
+      <c r="D9" s="260"/>
       <c r="E9" s="91" t="s">
         <v>115</v>
       </c>
@@ -18905,8 +18925,8 @@
       <c r="B10" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="265"/>
-      <c r="D10" s="262"/>
+      <c r="C10" s="263"/>
+      <c r="D10" s="260"/>
       <c r="E10" s="91" t="s">
         <v>188</v>
       </c>
@@ -18930,8 +18950,8 @@
       <c r="B11" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="265"/>
-      <c r="D11" s="262"/>
+      <c r="C11" s="263"/>
+      <c r="D11" s="260"/>
       <c r="E11" s="91" t="s">
         <v>200</v>
       </c>
@@ -18955,8 +18975,8 @@
       <c r="B12" s="91" t="s">
         <v>433</v>
       </c>
-      <c r="C12" s="266"/>
-      <c r="D12" s="263"/>
+      <c r="C12" s="264"/>
+      <c r="D12" s="261"/>
       <c r="E12" s="91" t="s">
         <v>213</v>
       </c>
@@ -18980,10 +19000,10 @@
       <c r="B13" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="268">
+      <c r="C13" s="266">
         <v>4</v>
       </c>
-      <c r="D13" s="270" t="s">
+      <c r="D13" s="268" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="91" t="s">
@@ -19007,8 +19027,8 @@
       <c r="B14" s="91" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="268"/>
-      <c r="D14" s="270"/>
+      <c r="C14" s="266"/>
+      <c r="D14" s="268"/>
       <c r="E14" s="91" t="s">
         <v>115</v>
       </c>
@@ -19028,8 +19048,8 @@
       <c r="B15" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="268"/>
-      <c r="D15" s="270"/>
+      <c r="C15" s="266"/>
+      <c r="D15" s="268"/>
       <c r="E15" s="91" t="s">
         <v>120</v>
       </c>
@@ -19049,8 +19069,8 @@
       <c r="B16" s="91" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="268"/>
-      <c r="D16" s="270"/>
+      <c r="C16" s="266"/>
+      <c r="D16" s="268"/>
       <c r="E16" s="91" t="s">
         <v>120</v>
       </c>
@@ -19070,8 +19090,8 @@
       <c r="B17" s="91" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="268"/>
-      <c r="D17" s="270"/>
+      <c r="C17" s="266"/>
+      <c r="D17" s="268"/>
       <c r="E17" s="91" t="s">
         <v>120</v>
       </c>
@@ -19091,10 +19111,10 @@
       <c r="B18" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="268">
+      <c r="C18" s="266">
         <v>5</v>
       </c>
-      <c r="D18" s="270" t="s">
+      <c r="D18" s="268" t="s">
         <v>113</v>
       </c>
       <c r="E18" s="91" t="s">
@@ -19118,8 +19138,8 @@
       <c r="B19" s="91" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="268"/>
-      <c r="D19" s="270"/>
+      <c r="C19" s="266"/>
+      <c r="D19" s="268"/>
       <c r="E19" s="91" t="s">
         <v>115</v>
       </c>
@@ -19139,8 +19159,8 @@
       <c r="B20" s="91" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="268"/>
-      <c r="D20" s="270"/>
+      <c r="C20" s="266"/>
+      <c r="D20" s="268"/>
       <c r="E20" s="91" t="s">
         <v>120</v>
       </c>
@@ -19160,8 +19180,8 @@
       <c r="B21" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="268"/>
-      <c r="D21" s="270"/>
+      <c r="C21" s="266"/>
+      <c r="D21" s="268"/>
       <c r="E21" s="91" t="s">
         <v>120</v>
       </c>
@@ -19181,8 +19201,8 @@
       <c r="B22" s="91" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="268"/>
-      <c r="D22" s="270"/>
+      <c r="C22" s="266"/>
+      <c r="D22" s="268"/>
       <c r="E22" s="91" t="s">
         <v>120</v>
       </c>
@@ -19202,10 +19222,10 @@
       <c r="B23" s="91" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="268">
+      <c r="C23" s="266">
         <v>6</v>
       </c>
-      <c r="D23" s="270" t="s">
+      <c r="D23" s="268" t="s">
         <v>113</v>
       </c>
       <c r="E23" s="91" t="s">
@@ -19229,8 +19249,8 @@
       <c r="B24" s="91" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="268"/>
-      <c r="D24" s="270"/>
+      <c r="C24" s="266"/>
+      <c r="D24" s="268"/>
       <c r="E24" s="91" t="s">
         <v>115</v>
       </c>
@@ -19250,8 +19270,8 @@
       <c r="B25" s="91" t="s">
         <v>179</v>
       </c>
-      <c r="C25" s="268"/>
-      <c r="D25" s="270"/>
+      <c r="C25" s="266"/>
+      <c r="D25" s="268"/>
       <c r="E25" s="91" t="s">
         <v>120</v>
       </c>
@@ -19271,8 +19291,8 @@
       <c r="B26" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="C26" s="268"/>
-      <c r="D26" s="270"/>
+      <c r="C26" s="266"/>
+      <c r="D26" s="268"/>
       <c r="E26" s="91" t="s">
         <v>120</v>
       </c>
@@ -19292,8 +19312,8 @@
       <c r="B27" s="91" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="268"/>
-      <c r="D27" s="270"/>
+      <c r="C27" s="266"/>
+      <c r="D27" s="268"/>
       <c r="E27" s="91" t="s">
         <v>120</v>
       </c>
@@ -19313,10 +19333,10 @@
       <c r="B28" s="91" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="268">
+      <c r="C28" s="266">
         <v>7</v>
       </c>
-      <c r="D28" s="270" t="s">
+      <c r="D28" s="268" t="s">
         <v>129</v>
       </c>
       <c r="E28" s="91" t="s">
@@ -19338,8 +19358,8 @@
       <c r="B29" s="91" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="268"/>
-      <c r="D29" s="270"/>
+      <c r="C29" s="266"/>
+      <c r="D29" s="268"/>
       <c r="E29" s="91" t="s">
         <v>120</v>
       </c>
@@ -19359,10 +19379,10 @@
       <c r="B30" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="268">
+      <c r="C30" s="266">
         <v>8</v>
       </c>
-      <c r="D30" s="270" t="s">
+      <c r="D30" s="268" t="s">
         <v>130</v>
       </c>
       <c r="E30" s="91" t="s">
@@ -19384,8 +19404,8 @@
       <c r="B31" s="95" t="s">
         <v>185</v>
       </c>
-      <c r="C31" s="269"/>
-      <c r="D31" s="271"/>
+      <c r="C31" s="267"/>
+      <c r="D31" s="269"/>
       <c r="E31" s="95" t="s">
         <v>120</v>
       </c>
@@ -19451,20 +19471,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="186" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="252"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="188"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="139" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="272" t="s">
+      <c r="B2" s="270" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="273"/>
+      <c r="C2" s="271"/>
       <c r="D2" s="159" t="s">
         <v>315</v>
       </c>
@@ -19473,10 +19493,10 @@
       <c r="A3" s="140" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="274" t="s">
+      <c r="B3" s="272" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="275"/>
+      <c r="C3" s="273"/>
       <c r="D3" s="160" t="s">
         <v>136</v>
       </c>
@@ -19485,19 +19505,19 @@
       <c r="A4" s="140" t="s">
         <v>246</v>
       </c>
-      <c r="B4" s="276" t="s">
+      <c r="B4" s="274" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="277"/>
+      <c r="C4" s="275"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1">
       <c r="A5" s="141" t="s">
         <v>245</v>
       </c>
-      <c r="B5" s="278" t="s">
+      <c r="B5" s="276" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="279"/>
+      <c r="C5" s="277"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" thickBot="1"/>
     <row r="7" spans="1:6" ht="17.25" thickBot="1">
@@ -19856,10 +19876,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42.75" customHeight="1">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="278" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="177"/>
+      <c r="B1" s="278"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="28" t="s">
